--- a/BWI/bestwine_output/bestwine_Sweden.xlsx
+++ b/BWI/bestwine_output/bestwine_Sweden.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA611"/>
+  <dimension ref="A1:AA612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -68831,6 +68831,99 @@
         </is>
       </c>
     </row>
+    <row r="612">
+      <c r="A612" s="2" t="inlineStr">
+        <is>
+          <t>Hübsch Vinhandel Ab</t>
+        </is>
+      </c>
+      <c r="B612" s="2" t="inlineStr">
+        <is>
+          <t>Hübsch Vinhandel Ab</t>
+        </is>
+      </c>
+      <c r="C612" s="2" t="inlineStr">
+        <is>
+          <t>25195</t>
+        </is>
+      </c>
+      <c r="D612" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E612" s="2" t="inlineStr">
+        <is>
+          <t>Bromma</t>
+        </is>
+      </c>
+      <c r="F612" s="2" t="inlineStr">
+        <is>
+          <t>Stockholms län</t>
+        </is>
+      </c>
+      <c r="G612" s="2" t="inlineStr">
+        <is>
+          <t>63 Doktor Abrahams Väg</t>
+        </is>
+      </c>
+      <c r="H612" s="2" t="inlineStr">
+        <is>
+          <t>168 59</t>
+        </is>
+      </c>
+      <c r="I612" s="2" t="inlineStr">
+        <is>
+          <t>https://hubschvinhandel.se</t>
+        </is>
+      </c>
+      <c r="J612" s="2" t="inlineStr"/>
+      <c r="K612" s="2" t="inlineStr"/>
+      <c r="L612" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M612" s="2" t="inlineStr"/>
+      <c r="N612" s="2" t="inlineStr">
+        <is>
+          <t>info@hubschvinhandel.se</t>
+        </is>
+      </c>
+      <c r="O612" s="2" t="inlineStr"/>
+      <c r="P612" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q612" s="2" t="inlineStr">
+        <is>
+          <t>5569489098</t>
+        </is>
+      </c>
+      <c r="R612" s="2" t="inlineStr"/>
+      <c r="S612" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hubschvinhandel</t>
+        </is>
+      </c>
+      <c r="T612" s="2" t="inlineStr"/>
+      <c r="U612" s="2" t="inlineStr"/>
+      <c r="V612" s="2" t="inlineStr"/>
+      <c r="W612" s="2" t="inlineStr">
+        <is>
+          <t>Göran Hübsch</t>
+        </is>
+      </c>
+      <c r="X612" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y612" s="2" t="inlineStr"/>
+      <c r="Z612" s="2" t="inlineStr"/>
+      <c r="AA612" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Sweden.xlsx
+++ b/BWI/bestwine_output/bestwine_Sweden.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA612"/>
+  <dimension ref="A1:AA617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -68924,6 +68924,543 @@
       <c r="Z612" s="2" t="inlineStr"/>
       <c r="AA612" s="2" t="inlineStr"/>
     </row>
+    <row r="613">
+      <c r="A613" s="2" t="inlineStr">
+        <is>
+          <t>Vinia Sweden Ab</t>
+        </is>
+      </c>
+      <c r="B613" s="2" t="inlineStr">
+        <is>
+          <t>Vinia Sweden Ab</t>
+        </is>
+      </c>
+      <c r="C613" s="2" t="inlineStr">
+        <is>
+          <t>12846</t>
+        </is>
+      </c>
+      <c r="D613" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E613" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F613" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G613" s="2" t="inlineStr">
+        <is>
+          <t>8 Gyllenstiernsgatan</t>
+        </is>
+      </c>
+      <c r="H613" s="2" t="inlineStr">
+        <is>
+          <t>115 26</t>
+        </is>
+      </c>
+      <c r="I613" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinia.se</t>
+        </is>
+      </c>
+      <c r="J613" s="2" t="inlineStr"/>
+      <c r="K613" s="2" t="inlineStr"/>
+      <c r="L613" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M613" s="2" t="inlineStr"/>
+      <c r="N613" s="2" t="inlineStr">
+        <is>
+          <t>info@vinia.se</t>
+        </is>
+      </c>
+      <c r="O613" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 732 59 95</t>
+        </is>
+      </c>
+      <c r="P613" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q613" s="2" t="inlineStr">
+        <is>
+          <t>5566906052</t>
+        </is>
+      </c>
+      <c r="R613" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinia-sweden-ab/</t>
+        </is>
+      </c>
+      <c r="S613" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Vinia-127868873799/</t>
+        </is>
+      </c>
+      <c r="T613" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viniasweden</t>
+        </is>
+      </c>
+      <c r="U613" s="2" t="inlineStr"/>
+      <c r="V613" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC7hui03EocS48wWL4cxSNUg</t>
+        </is>
+      </c>
+      <c r="W613" s="2" t="inlineStr">
+        <is>
+          <t>Per Engström</t>
+        </is>
+      </c>
+      <c r="X613" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y613" s="2" t="inlineStr"/>
+      <c r="Z613" s="2" t="inlineStr"/>
+      <c r="AA613" s="2" t="inlineStr">
+        <is>
+          <t>https://se.linkedin.com/pub/per-engstrom/3/283/b12</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="2" t="inlineStr">
+        <is>
+          <t>Vinia Sweden Ab</t>
+        </is>
+      </c>
+      <c r="B614" s="2" t="inlineStr">
+        <is>
+          <t>Vinia Sweden Ab</t>
+        </is>
+      </c>
+      <c r="C614" s="2" t="inlineStr">
+        <is>
+          <t>12846</t>
+        </is>
+      </c>
+      <c r="D614" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E614" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F614" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G614" s="2" t="inlineStr">
+        <is>
+          <t>8 Gyllenstiernsgatan</t>
+        </is>
+      </c>
+      <c r="H614" s="2" t="inlineStr">
+        <is>
+          <t>115 26</t>
+        </is>
+      </c>
+      <c r="I614" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinia.se</t>
+        </is>
+      </c>
+      <c r="J614" s="2" t="inlineStr"/>
+      <c r="K614" s="2" t="inlineStr"/>
+      <c r="L614" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M614" s="2" t="inlineStr"/>
+      <c r="N614" s="2" t="inlineStr">
+        <is>
+          <t>info@vinia.se</t>
+        </is>
+      </c>
+      <c r="O614" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 732 59 95</t>
+        </is>
+      </c>
+      <c r="P614" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q614" s="2" t="inlineStr">
+        <is>
+          <t>5566906052</t>
+        </is>
+      </c>
+      <c r="R614" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinia-sweden-ab/</t>
+        </is>
+      </c>
+      <c r="S614" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Vinia-127868873799/</t>
+        </is>
+      </c>
+      <c r="T614" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viniasweden</t>
+        </is>
+      </c>
+      <c r="U614" s="2" t="inlineStr"/>
+      <c r="V614" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC7hui03EocS48wWL4cxSNUg</t>
+        </is>
+      </c>
+      <c r="W614" s="2" t="inlineStr">
+        <is>
+          <t>Christina Nedfors</t>
+        </is>
+      </c>
+      <c r="X614" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager/ Administrations</t>
+        </is>
+      </c>
+      <c r="Y614" s="2" t="inlineStr"/>
+      <c r="Z614" s="2" t="inlineStr"/>
+      <c r="AA614" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/christina-nedfors-332629264/</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="2" t="inlineStr">
+        <is>
+          <t>Ward Wines Ab</t>
+        </is>
+      </c>
+      <c r="B615" s="2" t="inlineStr">
+        <is>
+          <t>Ward Wines Ab</t>
+        </is>
+      </c>
+      <c r="C615" s="2" t="inlineStr">
+        <is>
+          <t>12871</t>
+        </is>
+      </c>
+      <c r="D615" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E615" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F615" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G615" s="2" t="inlineStr">
+        <is>
+          <t>87D Östermalmsgatan</t>
+        </is>
+      </c>
+      <c r="H615" s="2" t="inlineStr">
+        <is>
+          <t>115 34</t>
+        </is>
+      </c>
+      <c r="I615" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wardwines.se</t>
+        </is>
+      </c>
+      <c r="J615" s="2" t="inlineStr"/>
+      <c r="K615" s="2" t="inlineStr"/>
+      <c r="L615" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M615" s="2" t="inlineStr"/>
+      <c r="N615" s="2" t="inlineStr">
+        <is>
+          <t>info@wardwines.se</t>
+        </is>
+      </c>
+      <c r="O615" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 511 698 30</t>
+        </is>
+      </c>
+      <c r="P615" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="Q615" s="2" t="inlineStr">
+        <is>
+          <t>5565055737</t>
+        </is>
+      </c>
+      <c r="R615" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ward-wines-ab/</t>
+        </is>
+      </c>
+      <c r="S615" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WardWines.AB</t>
+        </is>
+      </c>
+      <c r="T615" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ward_wines_vanner</t>
+        </is>
+      </c>
+      <c r="U615" s="2" t="inlineStr"/>
+      <c r="V615" s="2" t="inlineStr"/>
+      <c r="W615" s="2" t="inlineStr">
+        <is>
+          <t>Lisa Persson</t>
+        </is>
+      </c>
+      <c r="X615" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y615" s="2" t="inlineStr"/>
+      <c r="Z615" s="2" t="inlineStr"/>
+      <c r="AA615" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lisa-persson-b5635a27/</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="2" t="inlineStr">
+        <is>
+          <t>Ward Wines Ab</t>
+        </is>
+      </c>
+      <c r="B616" s="2" t="inlineStr">
+        <is>
+          <t>Ward Wines Ab</t>
+        </is>
+      </c>
+      <c r="C616" s="2" t="inlineStr">
+        <is>
+          <t>12871</t>
+        </is>
+      </c>
+      <c r="D616" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E616" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F616" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G616" s="2" t="inlineStr">
+        <is>
+          <t>87D Östermalmsgatan</t>
+        </is>
+      </c>
+      <c r="H616" s="2" t="inlineStr">
+        <is>
+          <t>115 34</t>
+        </is>
+      </c>
+      <c r="I616" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wardwines.se</t>
+        </is>
+      </c>
+      <c r="J616" s="2" t="inlineStr"/>
+      <c r="K616" s="2" t="inlineStr"/>
+      <c r="L616" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M616" s="2" t="inlineStr"/>
+      <c r="N616" s="2" t="inlineStr">
+        <is>
+          <t>info@wardwines.se</t>
+        </is>
+      </c>
+      <c r="O616" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 511 698 30</t>
+        </is>
+      </c>
+      <c r="P616" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="Q616" s="2" t="inlineStr">
+        <is>
+          <t>5565055737</t>
+        </is>
+      </c>
+      <c r="R616" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ward-wines-ab/</t>
+        </is>
+      </c>
+      <c r="S616" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WardWines.AB</t>
+        </is>
+      </c>
+      <c r="T616" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ward_wines_vanner</t>
+        </is>
+      </c>
+      <c r="U616" s="2" t="inlineStr"/>
+      <c r="V616" s="2" t="inlineStr"/>
+      <c r="W616" s="2" t="inlineStr">
+        <is>
+          <t>Malin Keyser</t>
+        </is>
+      </c>
+      <c r="X616" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y616" s="2" t="inlineStr"/>
+      <c r="Z616" s="2" t="inlineStr"/>
+      <c r="AA616" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/malin-keyser-8258298/</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="2" t="inlineStr">
+        <is>
+          <t>Hübsch Vinhandel Ab</t>
+        </is>
+      </c>
+      <c r="B617" s="2" t="inlineStr">
+        <is>
+          <t>Hübsch Vinhandel Ab</t>
+        </is>
+      </c>
+      <c r="C617" s="2" t="inlineStr">
+        <is>
+          <t>25195</t>
+        </is>
+      </c>
+      <c r="D617" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E617" s="2" t="inlineStr">
+        <is>
+          <t>Bromma</t>
+        </is>
+      </c>
+      <c r="F617" s="2" t="inlineStr">
+        <is>
+          <t>Stockholms län</t>
+        </is>
+      </c>
+      <c r="G617" s="2" t="inlineStr">
+        <is>
+          <t>63 Doktor Abrahams Väg</t>
+        </is>
+      </c>
+      <c r="H617" s="2" t="inlineStr">
+        <is>
+          <t>168 59</t>
+        </is>
+      </c>
+      <c r="I617" s="2" t="inlineStr">
+        <is>
+          <t>https://hubschvinhandel.se</t>
+        </is>
+      </c>
+      <c r="J617" s="2" t="inlineStr"/>
+      <c r="K617" s="2" t="inlineStr"/>
+      <c r="L617" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M617" s="2" t="inlineStr"/>
+      <c r="N617" s="2" t="inlineStr">
+        <is>
+          <t>info@hubschvinhandel.se</t>
+        </is>
+      </c>
+      <c r="O617" s="2" t="inlineStr"/>
+      <c r="P617" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q617" s="2" t="inlineStr">
+        <is>
+          <t>5569489098</t>
+        </is>
+      </c>
+      <c r="R617" s="2" t="inlineStr"/>
+      <c r="S617" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hubschvinhandel</t>
+        </is>
+      </c>
+      <c r="T617" s="2" t="inlineStr"/>
+      <c r="U617" s="2" t="inlineStr"/>
+      <c r="V617" s="2" t="inlineStr"/>
+      <c r="W617" s="2" t="inlineStr">
+        <is>
+          <t>Göran Hübsch</t>
+        </is>
+      </c>
+      <c r="X617" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y617" s="2" t="inlineStr"/>
+      <c r="Z617" s="2" t="inlineStr"/>
+      <c r="AA617" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Sweden.xlsx
+++ b/BWI/bestwine_output/bestwine_Sweden.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA617"/>
+  <dimension ref="A1:AA629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -69461,6 +69461,1266 @@
       <c r="Z617" s="2" t="inlineStr"/>
       <c r="AA617" s="2" t="inlineStr"/>
     </row>
+    <row r="618">
+      <c r="A618" s="2" t="inlineStr">
+        <is>
+          <t>Samplex Ab</t>
+        </is>
+      </c>
+      <c r="B618" s="2" t="inlineStr">
+        <is>
+          <t>Samplex Ab</t>
+        </is>
+      </c>
+      <c r="C618" s="2" t="inlineStr">
+        <is>
+          <t>12804</t>
+        </is>
+      </c>
+      <c r="D618" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E618" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F618" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="G618" s="2" t="inlineStr">
+        <is>
+          <t>3A Oxtorget</t>
+        </is>
+      </c>
+      <c r="H618" s="2" t="inlineStr">
+        <is>
+          <t>111 57</t>
+        </is>
+      </c>
+      <c r="I618" s="2" t="inlineStr">
+        <is>
+          <t>https://www.samplex.se</t>
+        </is>
+      </c>
+      <c r="J618" s="2" t="inlineStr"/>
+      <c r="K618" s="2" t="inlineStr"/>
+      <c r="L618" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M618" s="2" t="inlineStr"/>
+      <c r="N618" s="2" t="inlineStr">
+        <is>
+          <t>info@samplex.se</t>
+        </is>
+      </c>
+      <c r="O618" s="2" t="inlineStr"/>
+      <c r="P618" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q618" s="2" t="inlineStr">
+        <is>
+          <t>5564277472</t>
+        </is>
+      </c>
+      <c r="R618" s="2" t="inlineStr"/>
+      <c r="S618" s="2" t="inlineStr"/>
+      <c r="T618" s="2" t="inlineStr"/>
+      <c r="U618" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/samplexwines</t>
+        </is>
+      </c>
+      <c r="V618" s="2" t="inlineStr"/>
+      <c r="W618" s="2" t="inlineStr">
+        <is>
+          <t>Celine Xue Puttonen</t>
+        </is>
+      </c>
+      <c r="X618" s="2" t="inlineStr">
+        <is>
+          <t>Import &amp; Logistics Manager</t>
+        </is>
+      </c>
+      <c r="Y618" s="2" t="inlineStr"/>
+      <c r="Z618" s="2" t="inlineStr"/>
+      <c r="AA618" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/celine-xue-puttonen-6573931b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="2" t="inlineStr">
+        <is>
+          <t>Samplex Ab</t>
+        </is>
+      </c>
+      <c r="B619" s="2" t="inlineStr">
+        <is>
+          <t>Samplex Ab</t>
+        </is>
+      </c>
+      <c r="C619" s="2" t="inlineStr">
+        <is>
+          <t>12804</t>
+        </is>
+      </c>
+      <c r="D619" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E619" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F619" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="G619" s="2" t="inlineStr">
+        <is>
+          <t>3A Oxtorget</t>
+        </is>
+      </c>
+      <c r="H619" s="2" t="inlineStr">
+        <is>
+          <t>111 57</t>
+        </is>
+      </c>
+      <c r="I619" s="2" t="inlineStr">
+        <is>
+          <t>https://www.samplex.se</t>
+        </is>
+      </c>
+      <c r="J619" s="2" t="inlineStr"/>
+      <c r="K619" s="2" t="inlineStr"/>
+      <c r="L619" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M619" s="2" t="inlineStr"/>
+      <c r="N619" s="2" t="inlineStr">
+        <is>
+          <t>info@samplex.se</t>
+        </is>
+      </c>
+      <c r="O619" s="2" t="inlineStr"/>
+      <c r="P619" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q619" s="2" t="inlineStr">
+        <is>
+          <t>5564277472</t>
+        </is>
+      </c>
+      <c r="R619" s="2" t="inlineStr"/>
+      <c r="S619" s="2" t="inlineStr"/>
+      <c r="T619" s="2" t="inlineStr"/>
+      <c r="U619" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/samplexwines</t>
+        </is>
+      </c>
+      <c r="V619" s="2" t="inlineStr"/>
+      <c r="W619" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="X619" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y619" s="2" t="inlineStr"/>
+      <c r="Z619" s="2" t="inlineStr"/>
+      <c r="AA619" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/charlie-medvedor-hahne-b477ab8</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="2" t="inlineStr">
+        <is>
+          <t>Fine Brands Sweden Ab</t>
+        </is>
+      </c>
+      <c r="B620" s="2" t="inlineStr">
+        <is>
+          <t>Fine Brands Sweden Ab</t>
+        </is>
+      </c>
+      <c r="C620" s="2" t="inlineStr">
+        <is>
+          <t>12715</t>
+        </is>
+      </c>
+      <c r="D620" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E620" s="2" t="inlineStr">
+        <is>
+          <t>Kullavik</t>
+        </is>
+      </c>
+      <c r="F620" s="2" t="inlineStr">
+        <is>
+          <t>Hallands län</t>
+        </is>
+      </c>
+      <c r="G620" s="2" t="inlineStr">
+        <is>
+          <t>54 Hagenvägen</t>
+        </is>
+      </c>
+      <c r="H620" s="2" t="inlineStr">
+        <is>
+          <t>429 35</t>
+        </is>
+      </c>
+      <c r="I620" s="2" t="inlineStr">
+        <is>
+          <t>https://finebrands.se</t>
+        </is>
+      </c>
+      <c r="J620" s="2" t="inlineStr"/>
+      <c r="K620" s="2" t="inlineStr"/>
+      <c r="L620" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M620" s="2" t="inlineStr"/>
+      <c r="N620" s="2" t="inlineStr">
+        <is>
+          <t>info@finebrands.se</t>
+        </is>
+      </c>
+      <c r="O620" s="2" t="inlineStr">
+        <is>
+          <t>+46 31 313 31 93</t>
+        </is>
+      </c>
+      <c r="P620" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q620" s="2" t="inlineStr">
+        <is>
+          <t>5568328339</t>
+        </is>
+      </c>
+      <c r="R620" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fine-brands-sweden/</t>
+        </is>
+      </c>
+      <c r="S620" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Drinkseditor</t>
+        </is>
+      </c>
+      <c r="T620" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/finebrands/</t>
+        </is>
+      </c>
+      <c r="U620" s="2" t="inlineStr"/>
+      <c r="V620" s="2" t="inlineStr"/>
+      <c r="W620" s="2" t="inlineStr">
+        <is>
+          <t>Nicklas Ericson</t>
+        </is>
+      </c>
+      <c r="X620" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y620" s="2" t="inlineStr"/>
+      <c r="Z620" s="2" t="inlineStr"/>
+      <c r="AA620" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/nicklas-ericson-5793a546/</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="2" t="inlineStr">
+        <is>
+          <t>Iconic Wines Ab</t>
+        </is>
+      </c>
+      <c r="B621" s="2" t="inlineStr">
+        <is>
+          <t>Iconic Wines Ab</t>
+        </is>
+      </c>
+      <c r="C621" s="2" t="inlineStr">
+        <is>
+          <t>25194</t>
+        </is>
+      </c>
+      <c r="D621" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E621" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F621" s="2" t="inlineStr">
+        <is>
+          <t>Stockholms län</t>
+        </is>
+      </c>
+      <c r="G621" s="2" t="inlineStr">
+        <is>
+          <t>4A Blasieholmsgatan</t>
+        </is>
+      </c>
+      <c r="H621" s="2" t="inlineStr">
+        <is>
+          <t>111 48</t>
+        </is>
+      </c>
+      <c r="I621" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iconicwines.se</t>
+        </is>
+      </c>
+      <c r="J621" s="2" t="inlineStr"/>
+      <c r="K621" s="2" t="inlineStr"/>
+      <c r="L621" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M621" s="2" t="inlineStr"/>
+      <c r="N621" s="2" t="inlineStr">
+        <is>
+          <t>info@iconicwines.se</t>
+        </is>
+      </c>
+      <c r="O621" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 518 067 43</t>
+        </is>
+      </c>
+      <c r="P621" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q621" s="2" t="inlineStr">
+        <is>
+          <t>5590130471</t>
+        </is>
+      </c>
+      <c r="R621" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/iconic-wines/</t>
+        </is>
+      </c>
+      <c r="S621" s="2" t="inlineStr"/>
+      <c r="T621" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/iconic_wines/</t>
+        </is>
+      </c>
+      <c r="U621" s="2" t="inlineStr"/>
+      <c r="V621" s="2" t="inlineStr"/>
+      <c r="W621" s="2" t="inlineStr">
+        <is>
+          <t>Christian Borg</t>
+        </is>
+      </c>
+      <c r="X621" s="2" t="inlineStr">
+        <is>
+          <t>Purchaser</t>
+        </is>
+      </c>
+      <c r="Y621" s="2" t="inlineStr"/>
+      <c r="Z621" s="2" t="inlineStr"/>
+      <c r="AA621" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/christianborgsthlm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="inlineStr">
+        <is>
+          <t>Iconic Wines Ab</t>
+        </is>
+      </c>
+      <c r="B622" s="2" t="inlineStr">
+        <is>
+          <t>Iconic Wines Ab</t>
+        </is>
+      </c>
+      <c r="C622" s="2" t="inlineStr">
+        <is>
+          <t>25194</t>
+        </is>
+      </c>
+      <c r="D622" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E622" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F622" s="2" t="inlineStr">
+        <is>
+          <t>Stockholms län</t>
+        </is>
+      </c>
+      <c r="G622" s="2" t="inlineStr">
+        <is>
+          <t>4A Blasieholmsgatan</t>
+        </is>
+      </c>
+      <c r="H622" s="2" t="inlineStr">
+        <is>
+          <t>111 48</t>
+        </is>
+      </c>
+      <c r="I622" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iconicwines.se</t>
+        </is>
+      </c>
+      <c r="J622" s="2" t="inlineStr"/>
+      <c r="K622" s="2" t="inlineStr"/>
+      <c r="L622" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M622" s="2" t="inlineStr"/>
+      <c r="N622" s="2" t="inlineStr">
+        <is>
+          <t>info@iconicwines.se</t>
+        </is>
+      </c>
+      <c r="O622" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 518 067 43</t>
+        </is>
+      </c>
+      <c r="P622" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q622" s="2" t="inlineStr">
+        <is>
+          <t>5590130471</t>
+        </is>
+      </c>
+      <c r="R622" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/iconic-wines/</t>
+        </is>
+      </c>
+      <c r="S622" s="2" t="inlineStr"/>
+      <c r="T622" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/iconic_wines/</t>
+        </is>
+      </c>
+      <c r="U622" s="2" t="inlineStr"/>
+      <c r="V622" s="2" t="inlineStr"/>
+      <c r="W622" s="2" t="inlineStr">
+        <is>
+          <t>Ulrika Olivestedt</t>
+        </is>
+      </c>
+      <c r="X622" s="2" t="inlineStr">
+        <is>
+          <t>Purchaser</t>
+        </is>
+      </c>
+      <c r="Y622" s="2" t="inlineStr"/>
+      <c r="Z622" s="2" t="inlineStr"/>
+      <c r="AA622" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ulrika-olivestedt-7b494371/</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="2" t="inlineStr">
+        <is>
+          <t>VD Wines AB</t>
+        </is>
+      </c>
+      <c r="B623" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VD Wines </t>
+        </is>
+      </c>
+      <c r="C623" s="2" t="inlineStr">
+        <is>
+          <t>34056</t>
+        </is>
+      </c>
+      <c r="D623" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E623" s="2" t="inlineStr">
+        <is>
+          <t>Hägersten</t>
+        </is>
+      </c>
+      <c r="F623" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="G623" s="2" t="inlineStr">
+        <is>
+          <t>Båtsmanskroken 30</t>
+        </is>
+      </c>
+      <c r="H623" s="2" t="inlineStr">
+        <is>
+          <t>129 40</t>
+        </is>
+      </c>
+      <c r="I623" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vdwines.se</t>
+        </is>
+      </c>
+      <c r="J623" s="2" t="inlineStr"/>
+      <c r="K623" s="2" t="inlineStr"/>
+      <c r="L623" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M623" s="2" t="inlineStr">
+        <is>
+          <t>224124</t>
+        </is>
+      </c>
+      <c r="N623" s="2" t="inlineStr">
+        <is>
+          <t>viktor@vdwines.se</t>
+        </is>
+      </c>
+      <c r="O623" s="2" t="inlineStr"/>
+      <c r="P623" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q623" s="2" t="inlineStr">
+        <is>
+          <t>5567348015</t>
+        </is>
+      </c>
+      <c r="R623" s="2" t="inlineStr"/>
+      <c r="S623" s="2" t="inlineStr"/>
+      <c r="T623" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vd.wines/</t>
+        </is>
+      </c>
+      <c r="U623" s="2" t="inlineStr"/>
+      <c r="V623" s="2" t="inlineStr"/>
+      <c r="W623" s="2" t="inlineStr">
+        <is>
+          <t>Viktor Djurdjevic</t>
+        </is>
+      </c>
+      <c r="X623" s="2" t="inlineStr">
+        <is>
+          <t>Ceo &amp; Founder</t>
+        </is>
+      </c>
+      <c r="Y623" s="2" t="inlineStr"/>
+      <c r="Z623" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA623" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/viktor-djurdjevic-61731157/</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="inlineStr">
+        <is>
+          <t>Portucastas Ab</t>
+        </is>
+      </c>
+      <c r="B624" s="2" t="inlineStr">
+        <is>
+          <t>Portucastas Ab</t>
+        </is>
+      </c>
+      <c r="C624" s="2" t="inlineStr">
+        <is>
+          <t>12793</t>
+        </is>
+      </c>
+      <c r="D624" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E624" s="2" t="inlineStr">
+        <is>
+          <t>Selånger District</t>
+        </is>
+      </c>
+      <c r="F624" s="2" t="inlineStr">
+        <is>
+          <t>Vasternorrland</t>
+        </is>
+      </c>
+      <c r="G624" s="2" t="inlineStr">
+        <is>
+          <t>Västerro 214</t>
+        </is>
+      </c>
+      <c r="H624" s="2" t="inlineStr">
+        <is>
+          <t>855 91</t>
+        </is>
+      </c>
+      <c r="I624" s="2" t="inlineStr">
+        <is>
+          <t>https://portucastas.se</t>
+        </is>
+      </c>
+      <c r="J624" s="2" t="inlineStr"/>
+      <c r="K624" s="2" t="inlineStr"/>
+      <c r="L624" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M624" s="2" t="inlineStr"/>
+      <c r="N624" s="2" t="inlineStr">
+        <is>
+          <t>info@portucastas.se</t>
+        </is>
+      </c>
+      <c r="O624" s="2" t="inlineStr">
+        <is>
+          <t>+351 289 030 928</t>
+        </is>
+      </c>
+      <c r="P624" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q624" s="2" t="inlineStr">
+        <is>
+          <t>5566467253</t>
+        </is>
+      </c>
+      <c r="R624" s="2" t="inlineStr"/>
+      <c r="S624" s="2" t="inlineStr"/>
+      <c r="T624" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/portucastas/</t>
+        </is>
+      </c>
+      <c r="U624" s="2" t="inlineStr"/>
+      <c r="V624" s="2" t="inlineStr"/>
+      <c r="W624" s="2" t="inlineStr">
+        <is>
+          <t>Mattias Strömquist</t>
+        </is>
+      </c>
+      <c r="X624" s="2" t="inlineStr">
+        <is>
+          <t>Ceo/ Sales</t>
+        </is>
+      </c>
+      <c r="Y624" s="2" t="inlineStr"/>
+      <c r="Z624" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA624" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mattias-str%C3%B6mquist-09bab5153/</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="2" t="inlineStr">
+        <is>
+          <t>Vinia Sweden Ab</t>
+        </is>
+      </c>
+      <c r="B625" s="2" t="inlineStr">
+        <is>
+          <t>Vinia Sweden Ab</t>
+        </is>
+      </c>
+      <c r="C625" s="2" t="inlineStr">
+        <is>
+          <t>12846</t>
+        </is>
+      </c>
+      <c r="D625" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E625" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F625" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G625" s="2" t="inlineStr">
+        <is>
+          <t>8 Gyllenstiernsgatan</t>
+        </is>
+      </c>
+      <c r="H625" s="2" t="inlineStr">
+        <is>
+          <t>115 26</t>
+        </is>
+      </c>
+      <c r="I625" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinia.se</t>
+        </is>
+      </c>
+      <c r="J625" s="2" t="inlineStr"/>
+      <c r="K625" s="2" t="inlineStr"/>
+      <c r="L625" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M625" s="2" t="inlineStr"/>
+      <c r="N625" s="2" t="inlineStr">
+        <is>
+          <t>info@vinia.se</t>
+        </is>
+      </c>
+      <c r="O625" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 732 59 95</t>
+        </is>
+      </c>
+      <c r="P625" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q625" s="2" t="inlineStr">
+        <is>
+          <t>5566906052</t>
+        </is>
+      </c>
+      <c r="R625" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinia-sweden-ab/</t>
+        </is>
+      </c>
+      <c r="S625" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Vinia-127868873799/</t>
+        </is>
+      </c>
+      <c r="T625" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viniasweden</t>
+        </is>
+      </c>
+      <c r="U625" s="2" t="inlineStr"/>
+      <c r="V625" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC7hui03EocS48wWL4cxSNUg</t>
+        </is>
+      </c>
+      <c r="W625" s="2" t="inlineStr">
+        <is>
+          <t>Per Engström</t>
+        </is>
+      </c>
+      <c r="X625" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y625" s="2" t="inlineStr"/>
+      <c r="Z625" s="2" t="inlineStr"/>
+      <c r="AA625" s="2" t="inlineStr">
+        <is>
+          <t>https://se.linkedin.com/pub/per-engstrom/3/283/b12</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="2" t="inlineStr">
+        <is>
+          <t>Vinia Sweden Ab</t>
+        </is>
+      </c>
+      <c r="B626" s="2" t="inlineStr">
+        <is>
+          <t>Vinia Sweden Ab</t>
+        </is>
+      </c>
+      <c r="C626" s="2" t="inlineStr">
+        <is>
+          <t>12846</t>
+        </is>
+      </c>
+      <c r="D626" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E626" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F626" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G626" s="2" t="inlineStr">
+        <is>
+          <t>8 Gyllenstiernsgatan</t>
+        </is>
+      </c>
+      <c r="H626" s="2" t="inlineStr">
+        <is>
+          <t>115 26</t>
+        </is>
+      </c>
+      <c r="I626" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinia.se</t>
+        </is>
+      </c>
+      <c r="J626" s="2" t="inlineStr"/>
+      <c r="K626" s="2" t="inlineStr"/>
+      <c r="L626" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M626" s="2" t="inlineStr"/>
+      <c r="N626" s="2" t="inlineStr">
+        <is>
+          <t>info@vinia.se</t>
+        </is>
+      </c>
+      <c r="O626" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 732 59 95</t>
+        </is>
+      </c>
+      <c r="P626" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q626" s="2" t="inlineStr">
+        <is>
+          <t>5566906052</t>
+        </is>
+      </c>
+      <c r="R626" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinia-sweden-ab/</t>
+        </is>
+      </c>
+      <c r="S626" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Vinia-127868873799/</t>
+        </is>
+      </c>
+      <c r="T626" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viniasweden</t>
+        </is>
+      </c>
+      <c r="U626" s="2" t="inlineStr"/>
+      <c r="V626" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC7hui03EocS48wWL4cxSNUg</t>
+        </is>
+      </c>
+      <c r="W626" s="2" t="inlineStr">
+        <is>
+          <t>Christina Nedfors</t>
+        </is>
+      </c>
+      <c r="X626" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager/ Administrations</t>
+        </is>
+      </c>
+      <c r="Y626" s="2" t="inlineStr"/>
+      <c r="Z626" s="2" t="inlineStr"/>
+      <c r="AA626" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/christina-nedfors-332629264/</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="2" t="inlineStr">
+        <is>
+          <t>Ward Wines Ab</t>
+        </is>
+      </c>
+      <c r="B627" s="2" t="inlineStr">
+        <is>
+          <t>Ward Wines Ab</t>
+        </is>
+      </c>
+      <c r="C627" s="2" t="inlineStr">
+        <is>
+          <t>12871</t>
+        </is>
+      </c>
+      <c r="D627" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E627" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F627" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G627" s="2" t="inlineStr">
+        <is>
+          <t>87D Östermalmsgatan</t>
+        </is>
+      </c>
+      <c r="H627" s="2" t="inlineStr">
+        <is>
+          <t>115 34</t>
+        </is>
+      </c>
+      <c r="I627" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wardwines.se</t>
+        </is>
+      </c>
+      <c r="J627" s="2" t="inlineStr"/>
+      <c r="K627" s="2" t="inlineStr"/>
+      <c r="L627" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M627" s="2" t="inlineStr"/>
+      <c r="N627" s="2" t="inlineStr">
+        <is>
+          <t>info@wardwines.se</t>
+        </is>
+      </c>
+      <c r="O627" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 511 698 30</t>
+        </is>
+      </c>
+      <c r="P627" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="Q627" s="2" t="inlineStr">
+        <is>
+          <t>5565055737</t>
+        </is>
+      </c>
+      <c r="R627" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ward-wines-ab/</t>
+        </is>
+      </c>
+      <c r="S627" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WardWines.AB</t>
+        </is>
+      </c>
+      <c r="T627" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ward_wines_vanner</t>
+        </is>
+      </c>
+      <c r="U627" s="2" t="inlineStr"/>
+      <c r="V627" s="2" t="inlineStr"/>
+      <c r="W627" s="2" t="inlineStr">
+        <is>
+          <t>Lisa Persson</t>
+        </is>
+      </c>
+      <c r="X627" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y627" s="2" t="inlineStr"/>
+      <c r="Z627" s="2" t="inlineStr"/>
+      <c r="AA627" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lisa-persson-b5635a27/</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="2" t="inlineStr">
+        <is>
+          <t>Ward Wines Ab</t>
+        </is>
+      </c>
+      <c r="B628" s="2" t="inlineStr">
+        <is>
+          <t>Ward Wines Ab</t>
+        </is>
+      </c>
+      <c r="C628" s="2" t="inlineStr">
+        <is>
+          <t>12871</t>
+        </is>
+      </c>
+      <c r="D628" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E628" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F628" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G628" s="2" t="inlineStr">
+        <is>
+          <t>87D Östermalmsgatan</t>
+        </is>
+      </c>
+      <c r="H628" s="2" t="inlineStr">
+        <is>
+          <t>115 34</t>
+        </is>
+      </c>
+      <c r="I628" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wardwines.se</t>
+        </is>
+      </c>
+      <c r="J628" s="2" t="inlineStr"/>
+      <c r="K628" s="2" t="inlineStr"/>
+      <c r="L628" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M628" s="2" t="inlineStr"/>
+      <c r="N628" s="2" t="inlineStr">
+        <is>
+          <t>info@wardwines.se</t>
+        </is>
+      </c>
+      <c r="O628" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 511 698 30</t>
+        </is>
+      </c>
+      <c r="P628" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="Q628" s="2" t="inlineStr">
+        <is>
+          <t>5565055737</t>
+        </is>
+      </c>
+      <c r="R628" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ward-wines-ab/</t>
+        </is>
+      </c>
+      <c r="S628" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WardWines.AB</t>
+        </is>
+      </c>
+      <c r="T628" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ward_wines_vanner</t>
+        </is>
+      </c>
+      <c r="U628" s="2" t="inlineStr"/>
+      <c r="V628" s="2" t="inlineStr"/>
+      <c r="W628" s="2" t="inlineStr">
+        <is>
+          <t>Malin Keyser</t>
+        </is>
+      </c>
+      <c r="X628" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y628" s="2" t="inlineStr"/>
+      <c r="Z628" s="2" t="inlineStr"/>
+      <c r="AA628" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/malin-keyser-8258298/</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="2" t="inlineStr">
+        <is>
+          <t>Hübsch Vinhandel Ab</t>
+        </is>
+      </c>
+      <c r="B629" s="2" t="inlineStr">
+        <is>
+          <t>Hübsch Vinhandel Ab</t>
+        </is>
+      </c>
+      <c r="C629" s="2" t="inlineStr">
+        <is>
+          <t>25195</t>
+        </is>
+      </c>
+      <c r="D629" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E629" s="2" t="inlineStr">
+        <is>
+          <t>Bromma</t>
+        </is>
+      </c>
+      <c r="F629" s="2" t="inlineStr">
+        <is>
+          <t>Stockholms län</t>
+        </is>
+      </c>
+      <c r="G629" s="2" t="inlineStr">
+        <is>
+          <t>63 Doktor Abrahams Väg</t>
+        </is>
+      </c>
+      <c r="H629" s="2" t="inlineStr">
+        <is>
+          <t>168 59</t>
+        </is>
+      </c>
+      <c r="I629" s="2" t="inlineStr">
+        <is>
+          <t>https://hubschvinhandel.se</t>
+        </is>
+      </c>
+      <c r="J629" s="2" t="inlineStr"/>
+      <c r="K629" s="2" t="inlineStr"/>
+      <c r="L629" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M629" s="2" t="inlineStr"/>
+      <c r="N629" s="2" t="inlineStr">
+        <is>
+          <t>info@hubschvinhandel.se</t>
+        </is>
+      </c>
+      <c r="O629" s="2" t="inlineStr"/>
+      <c r="P629" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q629" s="2" t="inlineStr">
+        <is>
+          <t>5569489098</t>
+        </is>
+      </c>
+      <c r="R629" s="2" t="inlineStr"/>
+      <c r="S629" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hubschvinhandel</t>
+        </is>
+      </c>
+      <c r="T629" s="2" t="inlineStr"/>
+      <c r="U629" s="2" t="inlineStr"/>
+      <c r="V629" s="2" t="inlineStr"/>
+      <c r="W629" s="2" t="inlineStr">
+        <is>
+          <t>Göran Hübsch</t>
+        </is>
+      </c>
+      <c r="X629" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y629" s="2" t="inlineStr"/>
+      <c r="Z629" s="2" t="inlineStr"/>
+      <c r="AA629" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Sweden.xlsx
+++ b/BWI/bestwine_output/bestwine_Sweden.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA629"/>
+  <dimension ref="A1:AA663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -70721,6 +70721,3744 @@
       <c r="Z629" s="2" t="inlineStr"/>
       <c r="AA629" s="2" t="inlineStr"/>
     </row>
+    <row r="630">
+      <c r="A630" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="B630" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="C630" s="2" t="inlineStr">
+        <is>
+          <t>24493</t>
+        </is>
+      </c>
+      <c r="D630" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E630" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F630" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G630" s="2" t="inlineStr">
+        <is>
+          <t>Alsnögatan 11</t>
+        </is>
+      </c>
+      <c r="H630" s="2" t="inlineStr">
+        <is>
+          <t>116 44</t>
+        </is>
+      </c>
+      <c r="I630" s="2" t="inlineStr">
+        <is>
+          <t>https://www.enjoywine.se</t>
+        </is>
+      </c>
+      <c r="J630" s="2" t="inlineStr"/>
+      <c r="K630" s="2" t="inlineStr"/>
+      <c r="L630" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M630" s="2" t="inlineStr"/>
+      <c r="N630" s="2" t="inlineStr">
+        <is>
+          <t>info@enjoywine.se</t>
+        </is>
+      </c>
+      <c r="O630" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 556 947 00</t>
+        </is>
+      </c>
+      <c r="P630" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q630" s="2" t="inlineStr">
+        <is>
+          <t>5564577509</t>
+        </is>
+      </c>
+      <c r="R630" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enjoy-wine-and-spirits/</t>
+        </is>
+      </c>
+      <c r="S630" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enjoywine.se/</t>
+        </is>
+      </c>
+      <c r="T630" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enjoywineandspirits/</t>
+        </is>
+      </c>
+      <c r="U630" s="2" t="inlineStr"/>
+      <c r="V630" s="2" t="inlineStr"/>
+      <c r="W630" s="2" t="inlineStr">
+        <is>
+          <t>Anna Olsson</t>
+        </is>
+      </c>
+      <c r="X630" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y630" s="2" t="inlineStr"/>
+      <c r="Z630" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA630" s="2" t="inlineStr"/>
+    </row>
+    <row r="631">
+      <c r="A631" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="B631" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="C631" s="2" t="inlineStr">
+        <is>
+          <t>24493</t>
+        </is>
+      </c>
+      <c r="D631" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E631" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F631" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G631" s="2" t="inlineStr">
+        <is>
+          <t>Alsnögatan 11</t>
+        </is>
+      </c>
+      <c r="H631" s="2" t="inlineStr">
+        <is>
+          <t>116 44</t>
+        </is>
+      </c>
+      <c r="I631" s="2" t="inlineStr">
+        <is>
+          <t>https://www.enjoywine.se</t>
+        </is>
+      </c>
+      <c r="J631" s="2" t="inlineStr"/>
+      <c r="K631" s="2" t="inlineStr"/>
+      <c r="L631" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M631" s="2" t="inlineStr"/>
+      <c r="N631" s="2" t="inlineStr">
+        <is>
+          <t>info@enjoywine.se</t>
+        </is>
+      </c>
+      <c r="O631" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 556 947 00</t>
+        </is>
+      </c>
+      <c r="P631" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q631" s="2" t="inlineStr">
+        <is>
+          <t>5564577509</t>
+        </is>
+      </c>
+      <c r="R631" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enjoy-wine-and-spirits/</t>
+        </is>
+      </c>
+      <c r="S631" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enjoywine.se/</t>
+        </is>
+      </c>
+      <c r="T631" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enjoywineandspirits/</t>
+        </is>
+      </c>
+      <c r="U631" s="2" t="inlineStr"/>
+      <c r="V631" s="2" t="inlineStr"/>
+      <c r="W631" s="2" t="inlineStr">
+        <is>
+          <t>Johan Eklöf</t>
+        </is>
+      </c>
+      <c r="X631" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y631" s="2" t="inlineStr"/>
+      <c r="Z631" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA631" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/johan-eklof/</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="B632" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="C632" s="2" t="inlineStr">
+        <is>
+          <t>24493</t>
+        </is>
+      </c>
+      <c r="D632" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E632" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F632" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G632" s="2" t="inlineStr">
+        <is>
+          <t>Alsnögatan 11</t>
+        </is>
+      </c>
+      <c r="H632" s="2" t="inlineStr">
+        <is>
+          <t>116 44</t>
+        </is>
+      </c>
+      <c r="I632" s="2" t="inlineStr">
+        <is>
+          <t>https://www.enjoywine.se</t>
+        </is>
+      </c>
+      <c r="J632" s="2" t="inlineStr"/>
+      <c r="K632" s="2" t="inlineStr"/>
+      <c r="L632" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M632" s="2" t="inlineStr"/>
+      <c r="N632" s="2" t="inlineStr">
+        <is>
+          <t>info@enjoywine.se</t>
+        </is>
+      </c>
+      <c r="O632" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 556 947 00</t>
+        </is>
+      </c>
+      <c r="P632" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q632" s="2" t="inlineStr">
+        <is>
+          <t>5564577509</t>
+        </is>
+      </c>
+      <c r="R632" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enjoy-wine-and-spirits/</t>
+        </is>
+      </c>
+      <c r="S632" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enjoywine.se/</t>
+        </is>
+      </c>
+      <c r="T632" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enjoywineandspirits/</t>
+        </is>
+      </c>
+      <c r="U632" s="2" t="inlineStr"/>
+      <c r="V632" s="2" t="inlineStr"/>
+      <c r="W632" s="2" t="inlineStr">
+        <is>
+          <t>Simon Lidby</t>
+        </is>
+      </c>
+      <c r="X632" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y632" s="2" t="inlineStr"/>
+      <c r="Z632" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA632" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/simonlidby/</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="B633" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="C633" s="2" t="inlineStr">
+        <is>
+          <t>24493</t>
+        </is>
+      </c>
+      <c r="D633" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E633" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F633" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G633" s="2" t="inlineStr">
+        <is>
+          <t>Alsnögatan 11</t>
+        </is>
+      </c>
+      <c r="H633" s="2" t="inlineStr">
+        <is>
+          <t>116 44</t>
+        </is>
+      </c>
+      <c r="I633" s="2" t="inlineStr">
+        <is>
+          <t>https://www.enjoywine.se</t>
+        </is>
+      </c>
+      <c r="J633" s="2" t="inlineStr"/>
+      <c r="K633" s="2" t="inlineStr"/>
+      <c r="L633" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M633" s="2" t="inlineStr"/>
+      <c r="N633" s="2" t="inlineStr">
+        <is>
+          <t>info@enjoywine.se</t>
+        </is>
+      </c>
+      <c r="O633" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 556 947 00</t>
+        </is>
+      </c>
+      <c r="P633" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q633" s="2" t="inlineStr">
+        <is>
+          <t>5564577509</t>
+        </is>
+      </c>
+      <c r="R633" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enjoy-wine-and-spirits/</t>
+        </is>
+      </c>
+      <c r="S633" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enjoywine.se/</t>
+        </is>
+      </c>
+      <c r="T633" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enjoywineandspirits/</t>
+        </is>
+      </c>
+      <c r="U633" s="2" t="inlineStr"/>
+      <c r="V633" s="2" t="inlineStr"/>
+      <c r="W633" s="2" t="inlineStr">
+        <is>
+          <t>Sofia Lundahl</t>
+        </is>
+      </c>
+      <c r="X633" s="2" t="inlineStr">
+        <is>
+          <t>Business Controller</t>
+        </is>
+      </c>
+      <c r="Y633" s="2" t="inlineStr"/>
+      <c r="Z633" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA633" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sofia-lundahl-55682322/</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="B634" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="C634" s="2" t="inlineStr">
+        <is>
+          <t>24493</t>
+        </is>
+      </c>
+      <c r="D634" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E634" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F634" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G634" s="2" t="inlineStr">
+        <is>
+          <t>Alsnögatan 11</t>
+        </is>
+      </c>
+      <c r="H634" s="2" t="inlineStr">
+        <is>
+          <t>116 44</t>
+        </is>
+      </c>
+      <c r="I634" s="2" t="inlineStr">
+        <is>
+          <t>https://www.enjoywine.se</t>
+        </is>
+      </c>
+      <c r="J634" s="2" t="inlineStr"/>
+      <c r="K634" s="2" t="inlineStr"/>
+      <c r="L634" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M634" s="2" t="inlineStr"/>
+      <c r="N634" s="2" t="inlineStr">
+        <is>
+          <t>info@enjoywine.se</t>
+        </is>
+      </c>
+      <c r="O634" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 556 947 00</t>
+        </is>
+      </c>
+      <c r="P634" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q634" s="2" t="inlineStr">
+        <is>
+          <t>5564577509</t>
+        </is>
+      </c>
+      <c r="R634" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enjoy-wine-and-spirits/</t>
+        </is>
+      </c>
+      <c r="S634" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enjoywine.se/</t>
+        </is>
+      </c>
+      <c r="T634" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enjoywineandspirits/</t>
+        </is>
+      </c>
+      <c r="U634" s="2" t="inlineStr"/>
+      <c r="V634" s="2" t="inlineStr"/>
+      <c r="W634" s="2" t="inlineStr">
+        <is>
+          <t>Peter Kokovic</t>
+        </is>
+      </c>
+      <c r="X634" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y634" s="2" t="inlineStr"/>
+      <c r="Z634" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA634" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/peter-kokovic-b109667/</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="B635" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="C635" s="2" t="inlineStr">
+        <is>
+          <t>24493</t>
+        </is>
+      </c>
+      <c r="D635" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E635" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F635" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G635" s="2" t="inlineStr">
+        <is>
+          <t>Alsnögatan 11</t>
+        </is>
+      </c>
+      <c r="H635" s="2" t="inlineStr">
+        <is>
+          <t>116 44</t>
+        </is>
+      </c>
+      <c r="I635" s="2" t="inlineStr">
+        <is>
+          <t>https://www.enjoywine.se</t>
+        </is>
+      </c>
+      <c r="J635" s="2" t="inlineStr"/>
+      <c r="K635" s="2" t="inlineStr"/>
+      <c r="L635" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M635" s="2" t="inlineStr"/>
+      <c r="N635" s="2" t="inlineStr">
+        <is>
+          <t>info@enjoywine.se</t>
+        </is>
+      </c>
+      <c r="O635" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 556 947 00</t>
+        </is>
+      </c>
+      <c r="P635" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q635" s="2" t="inlineStr">
+        <is>
+          <t>5564577509</t>
+        </is>
+      </c>
+      <c r="R635" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enjoy-wine-and-spirits/</t>
+        </is>
+      </c>
+      <c r="S635" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enjoywine.se/</t>
+        </is>
+      </c>
+      <c r="T635" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enjoywineandspirits/</t>
+        </is>
+      </c>
+      <c r="U635" s="2" t="inlineStr"/>
+      <c r="V635" s="2" t="inlineStr"/>
+      <c r="W635" s="2" t="inlineStr">
+        <is>
+          <t>Maria Wästlund</t>
+        </is>
+      </c>
+      <c r="X635" s="2" t="inlineStr">
+        <is>
+          <t>Head of Marketing</t>
+        </is>
+      </c>
+      <c r="Y635" s="2" t="inlineStr"/>
+      <c r="Z635" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA635" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maria-w%C3%A4stlund-b949381/</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="B636" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="C636" s="2" t="inlineStr">
+        <is>
+          <t>24493</t>
+        </is>
+      </c>
+      <c r="D636" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E636" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F636" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G636" s="2" t="inlineStr">
+        <is>
+          <t>Alsnögatan 11</t>
+        </is>
+      </c>
+      <c r="H636" s="2" t="inlineStr">
+        <is>
+          <t>116 44</t>
+        </is>
+      </c>
+      <c r="I636" s="2" t="inlineStr">
+        <is>
+          <t>https://www.enjoywine.se</t>
+        </is>
+      </c>
+      <c r="J636" s="2" t="inlineStr"/>
+      <c r="K636" s="2" t="inlineStr"/>
+      <c r="L636" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M636" s="2" t="inlineStr"/>
+      <c r="N636" s="2" t="inlineStr">
+        <is>
+          <t>info@enjoywine.se</t>
+        </is>
+      </c>
+      <c r="O636" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 556 947 00</t>
+        </is>
+      </c>
+      <c r="P636" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q636" s="2" t="inlineStr">
+        <is>
+          <t>5564577509</t>
+        </is>
+      </c>
+      <c r="R636" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enjoy-wine-and-spirits/</t>
+        </is>
+      </c>
+      <c r="S636" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enjoywine.se/</t>
+        </is>
+      </c>
+      <c r="T636" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enjoywineandspirits/</t>
+        </is>
+      </c>
+      <c r="U636" s="2" t="inlineStr"/>
+      <c r="V636" s="2" t="inlineStr"/>
+      <c r="W636" s="2" t="inlineStr">
+        <is>
+          <t>Melker Ström</t>
+        </is>
+      </c>
+      <c r="X636" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Head of Products </t>
+        </is>
+      </c>
+      <c r="Y636" s="2" t="inlineStr"/>
+      <c r="Z636" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA636" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/melkers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="B637" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="C637" s="2" t="inlineStr">
+        <is>
+          <t>24493</t>
+        </is>
+      </c>
+      <c r="D637" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E637" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F637" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G637" s="2" t="inlineStr">
+        <is>
+          <t>Alsnögatan 11</t>
+        </is>
+      </c>
+      <c r="H637" s="2" t="inlineStr">
+        <is>
+          <t>116 44</t>
+        </is>
+      </c>
+      <c r="I637" s="2" t="inlineStr">
+        <is>
+          <t>https://www.enjoywine.se</t>
+        </is>
+      </c>
+      <c r="J637" s="2" t="inlineStr"/>
+      <c r="K637" s="2" t="inlineStr"/>
+      <c r="L637" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M637" s="2" t="inlineStr"/>
+      <c r="N637" s="2" t="inlineStr">
+        <is>
+          <t>info@enjoywine.se</t>
+        </is>
+      </c>
+      <c r="O637" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 556 947 00</t>
+        </is>
+      </c>
+      <c r="P637" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q637" s="2" t="inlineStr">
+        <is>
+          <t>5564577509</t>
+        </is>
+      </c>
+      <c r="R637" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enjoy-wine-and-spirits/</t>
+        </is>
+      </c>
+      <c r="S637" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enjoywine.se/</t>
+        </is>
+      </c>
+      <c r="T637" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enjoywineandspirits/</t>
+        </is>
+      </c>
+      <c r="U637" s="2" t="inlineStr"/>
+      <c r="V637" s="2" t="inlineStr"/>
+      <c r="W637" s="2" t="inlineStr">
+        <is>
+          <t>Johan Vincent</t>
+        </is>
+      </c>
+      <c r="X637" s="2" t="inlineStr">
+        <is>
+          <t>Key Account &amp; Wholsale Account Manager</t>
+        </is>
+      </c>
+      <c r="Y637" s="2" t="inlineStr"/>
+      <c r="Z637" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA637" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/johan-vincent-137b54a6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="B638" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="C638" s="2" t="inlineStr">
+        <is>
+          <t>24493</t>
+        </is>
+      </c>
+      <c r="D638" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E638" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F638" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G638" s="2" t="inlineStr">
+        <is>
+          <t>Alsnögatan 11</t>
+        </is>
+      </c>
+      <c r="H638" s="2" t="inlineStr">
+        <is>
+          <t>116 44</t>
+        </is>
+      </c>
+      <c r="I638" s="2" t="inlineStr">
+        <is>
+          <t>https://www.enjoywine.se</t>
+        </is>
+      </c>
+      <c r="J638" s="2" t="inlineStr"/>
+      <c r="K638" s="2" t="inlineStr"/>
+      <c r="L638" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M638" s="2" t="inlineStr"/>
+      <c r="N638" s="2" t="inlineStr">
+        <is>
+          <t>info@enjoywine.se</t>
+        </is>
+      </c>
+      <c r="O638" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 556 947 00</t>
+        </is>
+      </c>
+      <c r="P638" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q638" s="2" t="inlineStr">
+        <is>
+          <t>5564577509</t>
+        </is>
+      </c>
+      <c r="R638" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enjoy-wine-and-spirits/</t>
+        </is>
+      </c>
+      <c r="S638" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enjoywine.se/</t>
+        </is>
+      </c>
+      <c r="T638" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enjoywineandspirits/</t>
+        </is>
+      </c>
+      <c r="U638" s="2" t="inlineStr"/>
+      <c r="V638" s="2" t="inlineStr"/>
+      <c r="W638" s="2" t="inlineStr">
+        <is>
+          <t>Diana Strandberg</t>
+        </is>
+      </c>
+      <c r="X638" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Communications Manager</t>
+        </is>
+      </c>
+      <c r="Y638" s="2" t="inlineStr"/>
+      <c r="Z638" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA638" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/strandbergdiana/</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="B639" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="C639" s="2" t="inlineStr">
+        <is>
+          <t>24493</t>
+        </is>
+      </c>
+      <c r="D639" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E639" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F639" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G639" s="2" t="inlineStr">
+        <is>
+          <t>Alsnögatan 11</t>
+        </is>
+      </c>
+      <c r="H639" s="2" t="inlineStr">
+        <is>
+          <t>116 44</t>
+        </is>
+      </c>
+      <c r="I639" s="2" t="inlineStr">
+        <is>
+          <t>https://www.enjoywine.se</t>
+        </is>
+      </c>
+      <c r="J639" s="2" t="inlineStr"/>
+      <c r="K639" s="2" t="inlineStr"/>
+      <c r="L639" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M639" s="2" t="inlineStr"/>
+      <c r="N639" s="2" t="inlineStr">
+        <is>
+          <t>info@enjoywine.se</t>
+        </is>
+      </c>
+      <c r="O639" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 556 947 00</t>
+        </is>
+      </c>
+      <c r="P639" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q639" s="2" t="inlineStr">
+        <is>
+          <t>5564577509</t>
+        </is>
+      </c>
+      <c r="R639" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enjoy-wine-and-spirits/</t>
+        </is>
+      </c>
+      <c r="S639" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enjoywine.se/</t>
+        </is>
+      </c>
+      <c r="T639" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enjoywineandspirits/</t>
+        </is>
+      </c>
+      <c r="U639" s="2" t="inlineStr"/>
+      <c r="V639" s="2" t="inlineStr"/>
+      <c r="W639" s="2" t="inlineStr">
+        <is>
+          <t>Wilhelm Schultz</t>
+        </is>
+      </c>
+      <c r="X639" s="2" t="inlineStr">
+        <is>
+          <t>Owner &amp; Portfolio Manager Wine</t>
+        </is>
+      </c>
+      <c r="Y639" s="2" t="inlineStr"/>
+      <c r="Z639" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA639" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/wilhelm-schultz-b93b17a2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="B640" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="C640" s="2" t="inlineStr">
+        <is>
+          <t>24493</t>
+        </is>
+      </c>
+      <c r="D640" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E640" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F640" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G640" s="2" t="inlineStr">
+        <is>
+          <t>Alsnögatan 11</t>
+        </is>
+      </c>
+      <c r="H640" s="2" t="inlineStr">
+        <is>
+          <t>116 44</t>
+        </is>
+      </c>
+      <c r="I640" s="2" t="inlineStr">
+        <is>
+          <t>https://www.enjoywine.se</t>
+        </is>
+      </c>
+      <c r="J640" s="2" t="inlineStr"/>
+      <c r="K640" s="2" t="inlineStr"/>
+      <c r="L640" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M640" s="2" t="inlineStr"/>
+      <c r="N640" s="2" t="inlineStr">
+        <is>
+          <t>info@enjoywine.se</t>
+        </is>
+      </c>
+      <c r="O640" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 556 947 00</t>
+        </is>
+      </c>
+      <c r="P640" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q640" s="2" t="inlineStr">
+        <is>
+          <t>5564577509</t>
+        </is>
+      </c>
+      <c r="R640" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enjoy-wine-and-spirits/</t>
+        </is>
+      </c>
+      <c r="S640" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enjoywine.se/</t>
+        </is>
+      </c>
+      <c r="T640" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enjoywineandspirits/</t>
+        </is>
+      </c>
+      <c r="U640" s="2" t="inlineStr"/>
+      <c r="V640" s="2" t="inlineStr"/>
+      <c r="W640" s="2" t="inlineStr">
+        <is>
+          <t>David Ekenbäck</t>
+        </is>
+      </c>
+      <c r="X640" s="2" t="inlineStr">
+        <is>
+          <t>Product Development Manager</t>
+        </is>
+      </c>
+      <c r="Y640" s="2" t="inlineStr"/>
+      <c r="Z640" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA640" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-ekenb%C3%A4ck-76a7439/</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="B641" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="C641" s="2" t="inlineStr">
+        <is>
+          <t>24493</t>
+        </is>
+      </c>
+      <c r="D641" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E641" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F641" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G641" s="2" t="inlineStr">
+        <is>
+          <t>Alsnögatan 11</t>
+        </is>
+      </c>
+      <c r="H641" s="2" t="inlineStr">
+        <is>
+          <t>116 44</t>
+        </is>
+      </c>
+      <c r="I641" s="2" t="inlineStr">
+        <is>
+          <t>https://www.enjoywine.se</t>
+        </is>
+      </c>
+      <c r="J641" s="2" t="inlineStr"/>
+      <c r="K641" s="2" t="inlineStr"/>
+      <c r="L641" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M641" s="2" t="inlineStr"/>
+      <c r="N641" s="2" t="inlineStr">
+        <is>
+          <t>info@enjoywine.se</t>
+        </is>
+      </c>
+      <c r="O641" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 556 947 00</t>
+        </is>
+      </c>
+      <c r="P641" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q641" s="2" t="inlineStr">
+        <is>
+          <t>5564577509</t>
+        </is>
+      </c>
+      <c r="R641" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enjoy-wine-and-spirits/</t>
+        </is>
+      </c>
+      <c r="S641" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enjoywine.se/</t>
+        </is>
+      </c>
+      <c r="T641" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enjoywineandspirits/</t>
+        </is>
+      </c>
+      <c r="U641" s="2" t="inlineStr"/>
+      <c r="V641" s="2" t="inlineStr"/>
+      <c r="W641" s="2" t="inlineStr">
+        <is>
+          <t>Anna Danielsson</t>
+        </is>
+      </c>
+      <c r="X641" s="2" t="inlineStr">
+        <is>
+          <t>Purchase Coordinator</t>
+        </is>
+      </c>
+      <c r="Y641" s="2" t="inlineStr"/>
+      <c r="Z641" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA641" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anna-danielsson-2a502a45/</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="B642" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="C642" s="2" t="inlineStr">
+        <is>
+          <t>24493</t>
+        </is>
+      </c>
+      <c r="D642" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E642" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F642" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G642" s="2" t="inlineStr">
+        <is>
+          <t>Alsnögatan 11</t>
+        </is>
+      </c>
+      <c r="H642" s="2" t="inlineStr">
+        <is>
+          <t>116 44</t>
+        </is>
+      </c>
+      <c r="I642" s="2" t="inlineStr">
+        <is>
+          <t>https://www.enjoywine.se</t>
+        </is>
+      </c>
+      <c r="J642" s="2" t="inlineStr"/>
+      <c r="K642" s="2" t="inlineStr"/>
+      <c r="L642" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M642" s="2" t="inlineStr"/>
+      <c r="N642" s="2" t="inlineStr">
+        <is>
+          <t>info@enjoywine.se</t>
+        </is>
+      </c>
+      <c r="O642" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 556 947 00</t>
+        </is>
+      </c>
+      <c r="P642" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q642" s="2" t="inlineStr">
+        <is>
+          <t>5564577509</t>
+        </is>
+      </c>
+      <c r="R642" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enjoy-wine-and-spirits/</t>
+        </is>
+      </c>
+      <c r="S642" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enjoywine.se/</t>
+        </is>
+      </c>
+      <c r="T642" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enjoywineandspirits/</t>
+        </is>
+      </c>
+      <c r="U642" s="2" t="inlineStr"/>
+      <c r="V642" s="2" t="inlineStr"/>
+      <c r="W642" s="2" t="inlineStr">
+        <is>
+          <t>Mikaela Bremberg</t>
+        </is>
+      </c>
+      <c r="X642" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Manager</t>
+        </is>
+      </c>
+      <c r="Y642" s="2" t="inlineStr"/>
+      <c r="Z642" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA642" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mikaela-bremberg-8aa713185/</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="B643" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="C643" s="2" t="inlineStr">
+        <is>
+          <t>24493</t>
+        </is>
+      </c>
+      <c r="D643" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E643" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F643" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G643" s="2" t="inlineStr">
+        <is>
+          <t>Alsnögatan 11</t>
+        </is>
+      </c>
+      <c r="H643" s="2" t="inlineStr">
+        <is>
+          <t>116 44</t>
+        </is>
+      </c>
+      <c r="I643" s="2" t="inlineStr">
+        <is>
+          <t>https://www.enjoywine.se</t>
+        </is>
+      </c>
+      <c r="J643" s="2" t="inlineStr"/>
+      <c r="K643" s="2" t="inlineStr"/>
+      <c r="L643" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M643" s="2" t="inlineStr"/>
+      <c r="N643" s="2" t="inlineStr">
+        <is>
+          <t>info@enjoywine.se</t>
+        </is>
+      </c>
+      <c r="O643" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 556 947 00</t>
+        </is>
+      </c>
+      <c r="P643" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q643" s="2" t="inlineStr">
+        <is>
+          <t>5564577509</t>
+        </is>
+      </c>
+      <c r="R643" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enjoy-wine-and-spirits/</t>
+        </is>
+      </c>
+      <c r="S643" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enjoywine.se/</t>
+        </is>
+      </c>
+      <c r="T643" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enjoywineandspirits/</t>
+        </is>
+      </c>
+      <c r="U643" s="2" t="inlineStr"/>
+      <c r="V643" s="2" t="inlineStr"/>
+      <c r="W643" s="2" t="inlineStr">
+        <is>
+          <t>John Munkhammar</t>
+        </is>
+      </c>
+      <c r="X643" s="2" t="inlineStr">
+        <is>
+          <t>Supply Planner</t>
+        </is>
+      </c>
+      <c r="Y643" s="2" t="inlineStr"/>
+      <c r="Z643" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA643" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/john-munkhammar-a727b71b2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="B644" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="C644" s="2" t="inlineStr">
+        <is>
+          <t>24493</t>
+        </is>
+      </c>
+      <c r="D644" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E644" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F644" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G644" s="2" t="inlineStr">
+        <is>
+          <t>Alsnögatan 11</t>
+        </is>
+      </c>
+      <c r="H644" s="2" t="inlineStr">
+        <is>
+          <t>116 44</t>
+        </is>
+      </c>
+      <c r="I644" s="2" t="inlineStr">
+        <is>
+          <t>https://www.enjoywine.se</t>
+        </is>
+      </c>
+      <c r="J644" s="2" t="inlineStr"/>
+      <c r="K644" s="2" t="inlineStr"/>
+      <c r="L644" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M644" s="2" t="inlineStr"/>
+      <c r="N644" s="2" t="inlineStr">
+        <is>
+          <t>info@enjoywine.se</t>
+        </is>
+      </c>
+      <c r="O644" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 556 947 00</t>
+        </is>
+      </c>
+      <c r="P644" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q644" s="2" t="inlineStr">
+        <is>
+          <t>5564577509</t>
+        </is>
+      </c>
+      <c r="R644" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enjoy-wine-and-spirits/</t>
+        </is>
+      </c>
+      <c r="S644" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enjoywine.se/</t>
+        </is>
+      </c>
+      <c r="T644" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enjoywineandspirits/</t>
+        </is>
+      </c>
+      <c r="U644" s="2" t="inlineStr"/>
+      <c r="V644" s="2" t="inlineStr"/>
+      <c r="W644" s="2" t="inlineStr">
+        <is>
+          <t>Charlene Lima</t>
+        </is>
+      </c>
+      <c r="X644" s="2" t="inlineStr">
+        <is>
+          <t>Supply Planner</t>
+        </is>
+      </c>
+      <c r="Y644" s="2" t="inlineStr"/>
+      <c r="Z644" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA644" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/charlene-lima-146b31100/</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="B645" s="2" t="inlineStr">
+        <is>
+          <t>Enjoy Wine &amp; Spirits Ab</t>
+        </is>
+      </c>
+      <c r="C645" s="2" t="inlineStr">
+        <is>
+          <t>24493</t>
+        </is>
+      </c>
+      <c r="D645" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E645" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F645" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G645" s="2" t="inlineStr">
+        <is>
+          <t>Alsnögatan 11</t>
+        </is>
+      </c>
+      <c r="H645" s="2" t="inlineStr">
+        <is>
+          <t>116 44</t>
+        </is>
+      </c>
+      <c r="I645" s="2" t="inlineStr">
+        <is>
+          <t>https://www.enjoywine.se</t>
+        </is>
+      </c>
+      <c r="J645" s="2" t="inlineStr"/>
+      <c r="K645" s="2" t="inlineStr"/>
+      <c r="L645" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M645" s="2" t="inlineStr"/>
+      <c r="N645" s="2" t="inlineStr">
+        <is>
+          <t>info@enjoywine.se</t>
+        </is>
+      </c>
+      <c r="O645" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 556 947 00</t>
+        </is>
+      </c>
+      <c r="P645" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q645" s="2" t="inlineStr">
+        <is>
+          <t>5564577509</t>
+        </is>
+      </c>
+      <c r="R645" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/enjoy-wine-and-spirits/</t>
+        </is>
+      </c>
+      <c r="S645" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/enjoywine.se/</t>
+        </is>
+      </c>
+      <c r="T645" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/enjoywineandspirits/</t>
+        </is>
+      </c>
+      <c r="U645" s="2" t="inlineStr"/>
+      <c r="V645" s="2" t="inlineStr"/>
+      <c r="W645" s="2" t="inlineStr">
+        <is>
+          <t>Kristian Lindén</t>
+        </is>
+      </c>
+      <c r="X645" s="2" t="inlineStr">
+        <is>
+          <t>Head Of Sales</t>
+        </is>
+      </c>
+      <c r="Y645" s="2" t="inlineStr"/>
+      <c r="Z645" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA645" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kristian-lind%C3%A9n-77a8581/</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="2" t="inlineStr">
+        <is>
+          <t>Lively Wines Sweden Ab</t>
+        </is>
+      </c>
+      <c r="B646" s="2" t="inlineStr">
+        <is>
+          <t>Lively Wines Sweden Ab</t>
+        </is>
+      </c>
+      <c r="C646" s="2" t="inlineStr">
+        <is>
+          <t>12766</t>
+        </is>
+      </c>
+      <c r="D646" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E646" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F646" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="G646" s="2" t="inlineStr">
+        <is>
+          <t>Rörstrandsgatan 18</t>
+        </is>
+      </c>
+      <c r="H646" s="2" t="inlineStr">
+        <is>
+          <t>113 40</t>
+        </is>
+      </c>
+      <c r="I646" s="2" t="inlineStr">
+        <is>
+          <t>https://livelywines.se</t>
+        </is>
+      </c>
+      <c r="J646" s="2" t="inlineStr"/>
+      <c r="K646" s="2" t="inlineStr"/>
+      <c r="L646" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M646" s="2" t="inlineStr"/>
+      <c r="N646" s="2" t="inlineStr">
+        <is>
+          <t>info@livelywines.se</t>
+        </is>
+      </c>
+      <c r="O646" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 562 262 28</t>
+        </is>
+      </c>
+      <c r="P646" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q646" s="2" t="inlineStr">
+        <is>
+          <t>5569674434</t>
+        </is>
+      </c>
+      <c r="R646" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lively-wines-sweden/</t>
+        </is>
+      </c>
+      <c r="S646" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/livelywine/</t>
+        </is>
+      </c>
+      <c r="T646" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/livelywinessweden</t>
+        </is>
+      </c>
+      <c r="U646" s="2" t="inlineStr"/>
+      <c r="V646" s="2" t="inlineStr"/>
+      <c r="W646" s="2" t="inlineStr">
+        <is>
+          <t>Fredrik Bengtsson</t>
+        </is>
+      </c>
+      <c r="X646" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y646" s="2" t="inlineStr"/>
+      <c r="Z646" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA646" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fredrik-bengtsson-6417512/</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="2" t="inlineStr">
+        <is>
+          <t>Lively Wines Sweden Ab</t>
+        </is>
+      </c>
+      <c r="B647" s="2" t="inlineStr">
+        <is>
+          <t>Lively Wines Sweden Ab</t>
+        </is>
+      </c>
+      <c r="C647" s="2" t="inlineStr">
+        <is>
+          <t>12766</t>
+        </is>
+      </c>
+      <c r="D647" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E647" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F647" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="G647" s="2" t="inlineStr">
+        <is>
+          <t>Rörstrandsgatan 18</t>
+        </is>
+      </c>
+      <c r="H647" s="2" t="inlineStr">
+        <is>
+          <t>113 40</t>
+        </is>
+      </c>
+      <c r="I647" s="2" t="inlineStr">
+        <is>
+          <t>https://livelywines.se</t>
+        </is>
+      </c>
+      <c r="J647" s="2" t="inlineStr"/>
+      <c r="K647" s="2" t="inlineStr"/>
+      <c r="L647" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M647" s="2" t="inlineStr"/>
+      <c r="N647" s="2" t="inlineStr">
+        <is>
+          <t>info@livelywines.se</t>
+        </is>
+      </c>
+      <c r="O647" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 562 262 28</t>
+        </is>
+      </c>
+      <c r="P647" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q647" s="2" t="inlineStr">
+        <is>
+          <t>5569674434</t>
+        </is>
+      </c>
+      <c r="R647" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lively-wines-sweden/</t>
+        </is>
+      </c>
+      <c r="S647" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/livelywine/</t>
+        </is>
+      </c>
+      <c r="T647" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/livelywinessweden</t>
+        </is>
+      </c>
+      <c r="U647" s="2" t="inlineStr"/>
+      <c r="V647" s="2" t="inlineStr"/>
+      <c r="W647" s="2" t="inlineStr">
+        <is>
+          <t>William Möller</t>
+        </is>
+      </c>
+      <c r="X647" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="Y647" s="2" t="inlineStr"/>
+      <c r="Z647" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA647" s="2" t="inlineStr"/>
+    </row>
+    <row r="648">
+      <c r="A648" s="2" t="inlineStr">
+        <is>
+          <t>Lively Wines Sweden Ab</t>
+        </is>
+      </c>
+      <c r="B648" s="2" t="inlineStr">
+        <is>
+          <t>Lively Wines Sweden Ab</t>
+        </is>
+      </c>
+      <c r="C648" s="2" t="inlineStr">
+        <is>
+          <t>12766</t>
+        </is>
+      </c>
+      <c r="D648" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E648" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F648" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="G648" s="2" t="inlineStr">
+        <is>
+          <t>Rörstrandsgatan 18</t>
+        </is>
+      </c>
+      <c r="H648" s="2" t="inlineStr">
+        <is>
+          <t>113 40</t>
+        </is>
+      </c>
+      <c r="I648" s="2" t="inlineStr">
+        <is>
+          <t>https://livelywines.se</t>
+        </is>
+      </c>
+      <c r="J648" s="2" t="inlineStr"/>
+      <c r="K648" s="2" t="inlineStr"/>
+      <c r="L648" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M648" s="2" t="inlineStr"/>
+      <c r="N648" s="2" t="inlineStr">
+        <is>
+          <t>info@livelywines.se</t>
+        </is>
+      </c>
+      <c r="O648" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 562 262 28</t>
+        </is>
+      </c>
+      <c r="P648" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q648" s="2" t="inlineStr">
+        <is>
+          <t>5569674434</t>
+        </is>
+      </c>
+      <c r="R648" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lively-wines-sweden/</t>
+        </is>
+      </c>
+      <c r="S648" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/livelywine/</t>
+        </is>
+      </c>
+      <c r="T648" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/livelywinessweden</t>
+        </is>
+      </c>
+      <c r="U648" s="2" t="inlineStr"/>
+      <c r="V648" s="2" t="inlineStr"/>
+      <c r="W648" s="2" t="inlineStr">
+        <is>
+          <t>Anette Liljeberg</t>
+        </is>
+      </c>
+      <c r="X648" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y648" s="2" t="inlineStr"/>
+      <c r="Z648" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA648" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anette-liljeberg-59146bb8/</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="2" t="inlineStr">
+        <is>
+          <t>Lively Wines Sweden Ab</t>
+        </is>
+      </c>
+      <c r="B649" s="2" t="inlineStr">
+        <is>
+          <t>Lively Wines Sweden Ab</t>
+        </is>
+      </c>
+      <c r="C649" s="2" t="inlineStr">
+        <is>
+          <t>12766</t>
+        </is>
+      </c>
+      <c r="D649" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E649" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F649" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="G649" s="2" t="inlineStr">
+        <is>
+          <t>Rörstrandsgatan 18</t>
+        </is>
+      </c>
+      <c r="H649" s="2" t="inlineStr">
+        <is>
+          <t>113 40</t>
+        </is>
+      </c>
+      <c r="I649" s="2" t="inlineStr">
+        <is>
+          <t>https://livelywines.se</t>
+        </is>
+      </c>
+      <c r="J649" s="2" t="inlineStr"/>
+      <c r="K649" s="2" t="inlineStr"/>
+      <c r="L649" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M649" s="2" t="inlineStr"/>
+      <c r="N649" s="2" t="inlineStr">
+        <is>
+          <t>info@livelywines.se</t>
+        </is>
+      </c>
+      <c r="O649" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 562 262 28</t>
+        </is>
+      </c>
+      <c r="P649" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q649" s="2" t="inlineStr">
+        <is>
+          <t>5569674434</t>
+        </is>
+      </c>
+      <c r="R649" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lively-wines-sweden/</t>
+        </is>
+      </c>
+      <c r="S649" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/livelywine/</t>
+        </is>
+      </c>
+      <c r="T649" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/livelywinessweden</t>
+        </is>
+      </c>
+      <c r="U649" s="2" t="inlineStr"/>
+      <c r="V649" s="2" t="inlineStr"/>
+      <c r="W649" s="2" t="inlineStr">
+        <is>
+          <t>Alessio Piazza</t>
+        </is>
+      </c>
+      <c r="X649" s="2" t="inlineStr">
+        <is>
+          <t>Senior Product Manager</t>
+        </is>
+      </c>
+      <c r="Y649" s="2" t="inlineStr"/>
+      <c r="Z649" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA649" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alessiopiazza/</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="2" t="inlineStr">
+        <is>
+          <t>Lively Wines Sweden Ab</t>
+        </is>
+      </c>
+      <c r="B650" s="2" t="inlineStr">
+        <is>
+          <t>Lively Wines Sweden Ab</t>
+        </is>
+      </c>
+      <c r="C650" s="2" t="inlineStr">
+        <is>
+          <t>12766</t>
+        </is>
+      </c>
+      <c r="D650" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E650" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F650" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="G650" s="2" t="inlineStr">
+        <is>
+          <t>Rörstrandsgatan 18</t>
+        </is>
+      </c>
+      <c r="H650" s="2" t="inlineStr">
+        <is>
+          <t>113 40</t>
+        </is>
+      </c>
+      <c r="I650" s="2" t="inlineStr">
+        <is>
+          <t>https://livelywines.se</t>
+        </is>
+      </c>
+      <c r="J650" s="2" t="inlineStr"/>
+      <c r="K650" s="2" t="inlineStr"/>
+      <c r="L650" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M650" s="2" t="inlineStr"/>
+      <c r="N650" s="2" t="inlineStr">
+        <is>
+          <t>info@livelywines.se</t>
+        </is>
+      </c>
+      <c r="O650" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 562 262 28</t>
+        </is>
+      </c>
+      <c r="P650" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q650" s="2" t="inlineStr">
+        <is>
+          <t>5569674434</t>
+        </is>
+      </c>
+      <c r="R650" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lively-wines-sweden/</t>
+        </is>
+      </c>
+      <c r="S650" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/livelywine/</t>
+        </is>
+      </c>
+      <c r="T650" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/livelywinessweden</t>
+        </is>
+      </c>
+      <c r="U650" s="2" t="inlineStr"/>
+      <c r="V650" s="2" t="inlineStr"/>
+      <c r="W650" s="2" t="inlineStr">
+        <is>
+          <t>Annica Bondelid</t>
+        </is>
+      </c>
+      <c r="X650" s="2" t="inlineStr">
+        <is>
+          <t>Senior Product Manager</t>
+        </is>
+      </c>
+      <c r="Y650" s="2" t="inlineStr"/>
+      <c r="Z650" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA650" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/annica-bondelid-a233b313/</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="2" t="inlineStr">
+        <is>
+          <t>Lively Wines Sweden Ab</t>
+        </is>
+      </c>
+      <c r="B651" s="2" t="inlineStr">
+        <is>
+          <t>Lively Wines Sweden Ab</t>
+        </is>
+      </c>
+      <c r="C651" s="2" t="inlineStr">
+        <is>
+          <t>12766</t>
+        </is>
+      </c>
+      <c r="D651" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E651" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F651" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="G651" s="2" t="inlineStr">
+        <is>
+          <t>Rörstrandsgatan 18</t>
+        </is>
+      </c>
+      <c r="H651" s="2" t="inlineStr">
+        <is>
+          <t>113 40</t>
+        </is>
+      </c>
+      <c r="I651" s="2" t="inlineStr">
+        <is>
+          <t>https://livelywines.se</t>
+        </is>
+      </c>
+      <c r="J651" s="2" t="inlineStr"/>
+      <c r="K651" s="2" t="inlineStr"/>
+      <c r="L651" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M651" s="2" t="inlineStr"/>
+      <c r="N651" s="2" t="inlineStr">
+        <is>
+          <t>info@livelywines.se</t>
+        </is>
+      </c>
+      <c r="O651" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 562 262 28</t>
+        </is>
+      </c>
+      <c r="P651" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q651" s="2" t="inlineStr">
+        <is>
+          <t>5569674434</t>
+        </is>
+      </c>
+      <c r="R651" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lively-wines-sweden/</t>
+        </is>
+      </c>
+      <c r="S651" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/livelywine/</t>
+        </is>
+      </c>
+      <c r="T651" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/livelywinessweden</t>
+        </is>
+      </c>
+      <c r="U651" s="2" t="inlineStr"/>
+      <c r="V651" s="2" t="inlineStr"/>
+      <c r="W651" s="2" t="inlineStr">
+        <is>
+          <t>Henrik Björck</t>
+        </is>
+      </c>
+      <c r="X651" s="2" t="inlineStr">
+        <is>
+          <t>Director And Partner</t>
+        </is>
+      </c>
+      <c r="Y651" s="2" t="inlineStr"/>
+      <c r="Z651" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA651" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/henrik-bj%C3%B6rck-220a0586/</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="2" t="inlineStr">
+        <is>
+          <t>Samplex Ab</t>
+        </is>
+      </c>
+      <c r="B652" s="2" t="inlineStr">
+        <is>
+          <t>Samplex Ab</t>
+        </is>
+      </c>
+      <c r="C652" s="2" t="inlineStr">
+        <is>
+          <t>12804</t>
+        </is>
+      </c>
+      <c r="D652" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E652" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F652" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="G652" s="2" t="inlineStr">
+        <is>
+          <t>3A Oxtorget</t>
+        </is>
+      </c>
+      <c r="H652" s="2" t="inlineStr">
+        <is>
+          <t>111 57</t>
+        </is>
+      </c>
+      <c r="I652" s="2" t="inlineStr">
+        <is>
+          <t>https://www.samplex.se</t>
+        </is>
+      </c>
+      <c r="J652" s="2" t="inlineStr"/>
+      <c r="K652" s="2" t="inlineStr"/>
+      <c r="L652" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M652" s="2" t="inlineStr"/>
+      <c r="N652" s="2" t="inlineStr">
+        <is>
+          <t>info@samplex.se</t>
+        </is>
+      </c>
+      <c r="O652" s="2" t="inlineStr"/>
+      <c r="P652" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q652" s="2" t="inlineStr">
+        <is>
+          <t>5564277472</t>
+        </is>
+      </c>
+      <c r="R652" s="2" t="inlineStr"/>
+      <c r="S652" s="2" t="inlineStr"/>
+      <c r="T652" s="2" t="inlineStr"/>
+      <c r="U652" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/samplexwines</t>
+        </is>
+      </c>
+      <c r="V652" s="2" t="inlineStr"/>
+      <c r="W652" s="2" t="inlineStr">
+        <is>
+          <t>Celine Xue Puttonen</t>
+        </is>
+      </c>
+      <c r="X652" s="2" t="inlineStr">
+        <is>
+          <t>Import &amp; Logistics Manager</t>
+        </is>
+      </c>
+      <c r="Y652" s="2" t="inlineStr"/>
+      <c r="Z652" s="2" t="inlineStr"/>
+      <c r="AA652" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/celine-xue-puttonen-6573931b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="2" t="inlineStr">
+        <is>
+          <t>Samplex Ab</t>
+        </is>
+      </c>
+      <c r="B653" s="2" t="inlineStr">
+        <is>
+          <t>Samplex Ab</t>
+        </is>
+      </c>
+      <c r="C653" s="2" t="inlineStr">
+        <is>
+          <t>12804</t>
+        </is>
+      </c>
+      <c r="D653" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E653" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F653" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="G653" s="2" t="inlineStr">
+        <is>
+          <t>3A Oxtorget</t>
+        </is>
+      </c>
+      <c r="H653" s="2" t="inlineStr">
+        <is>
+          <t>111 57</t>
+        </is>
+      </c>
+      <c r="I653" s="2" t="inlineStr">
+        <is>
+          <t>https://www.samplex.se</t>
+        </is>
+      </c>
+      <c r="J653" s="2" t="inlineStr"/>
+      <c r="K653" s="2" t="inlineStr"/>
+      <c r="L653" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M653" s="2" t="inlineStr"/>
+      <c r="N653" s="2" t="inlineStr">
+        <is>
+          <t>info@samplex.se</t>
+        </is>
+      </c>
+      <c r="O653" s="2" t="inlineStr"/>
+      <c r="P653" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q653" s="2" t="inlineStr">
+        <is>
+          <t>5564277472</t>
+        </is>
+      </c>
+      <c r="R653" s="2" t="inlineStr"/>
+      <c r="S653" s="2" t="inlineStr"/>
+      <c r="T653" s="2" t="inlineStr"/>
+      <c r="U653" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/samplexwines</t>
+        </is>
+      </c>
+      <c r="V653" s="2" t="inlineStr"/>
+      <c r="W653" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="X653" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y653" s="2" t="inlineStr"/>
+      <c r="Z653" s="2" t="inlineStr"/>
+      <c r="AA653" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/charlie-medvedor-hahne-b477ab8</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="2" t="inlineStr">
+        <is>
+          <t>Fine Brands Sweden Ab</t>
+        </is>
+      </c>
+      <c r="B654" s="2" t="inlineStr">
+        <is>
+          <t>Fine Brands Sweden Ab</t>
+        </is>
+      </c>
+      <c r="C654" s="2" t="inlineStr">
+        <is>
+          <t>12715</t>
+        </is>
+      </c>
+      <c r="D654" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E654" s="2" t="inlineStr">
+        <is>
+          <t>Kullavik</t>
+        </is>
+      </c>
+      <c r="F654" s="2" t="inlineStr">
+        <is>
+          <t>Hallands län</t>
+        </is>
+      </c>
+      <c r="G654" s="2" t="inlineStr">
+        <is>
+          <t>54 Hagenvägen</t>
+        </is>
+      </c>
+      <c r="H654" s="2" t="inlineStr">
+        <is>
+          <t>429 35</t>
+        </is>
+      </c>
+      <c r="I654" s="2" t="inlineStr">
+        <is>
+          <t>https://finebrands.se</t>
+        </is>
+      </c>
+      <c r="J654" s="2" t="inlineStr"/>
+      <c r="K654" s="2" t="inlineStr"/>
+      <c r="L654" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M654" s="2" t="inlineStr"/>
+      <c r="N654" s="2" t="inlineStr">
+        <is>
+          <t>info@finebrands.se</t>
+        </is>
+      </c>
+      <c r="O654" s="2" t="inlineStr">
+        <is>
+          <t>+46 31 313 31 93</t>
+        </is>
+      </c>
+      <c r="P654" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q654" s="2" t="inlineStr">
+        <is>
+          <t>5568328339</t>
+        </is>
+      </c>
+      <c r="R654" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fine-brands-sweden/</t>
+        </is>
+      </c>
+      <c r="S654" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Drinkseditor</t>
+        </is>
+      </c>
+      <c r="T654" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/finebrands/</t>
+        </is>
+      </c>
+      <c r="U654" s="2" t="inlineStr"/>
+      <c r="V654" s="2" t="inlineStr"/>
+      <c r="W654" s="2" t="inlineStr">
+        <is>
+          <t>Nicklas Ericson</t>
+        </is>
+      </c>
+      <c r="X654" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y654" s="2" t="inlineStr"/>
+      <c r="Z654" s="2" t="inlineStr"/>
+      <c r="AA654" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/nicklas-ericson-5793a546/</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="2" t="inlineStr">
+        <is>
+          <t>Iconic Wines Ab</t>
+        </is>
+      </c>
+      <c r="B655" s="2" t="inlineStr">
+        <is>
+          <t>Iconic Wines Ab</t>
+        </is>
+      </c>
+      <c r="C655" s="2" t="inlineStr">
+        <is>
+          <t>25194</t>
+        </is>
+      </c>
+      <c r="D655" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E655" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F655" s="2" t="inlineStr">
+        <is>
+          <t>Stockholms län</t>
+        </is>
+      </c>
+      <c r="G655" s="2" t="inlineStr">
+        <is>
+          <t>4A Blasieholmsgatan</t>
+        </is>
+      </c>
+      <c r="H655" s="2" t="inlineStr">
+        <is>
+          <t>111 48</t>
+        </is>
+      </c>
+      <c r="I655" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iconicwines.se</t>
+        </is>
+      </c>
+      <c r="J655" s="2" t="inlineStr"/>
+      <c r="K655" s="2" t="inlineStr"/>
+      <c r="L655" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M655" s="2" t="inlineStr"/>
+      <c r="N655" s="2" t="inlineStr">
+        <is>
+          <t>info@iconicwines.se</t>
+        </is>
+      </c>
+      <c r="O655" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 518 067 43</t>
+        </is>
+      </c>
+      <c r="P655" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q655" s="2" t="inlineStr">
+        <is>
+          <t>5590130471</t>
+        </is>
+      </c>
+      <c r="R655" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/iconic-wines/</t>
+        </is>
+      </c>
+      <c r="S655" s="2" t="inlineStr"/>
+      <c r="T655" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/iconic_wines/</t>
+        </is>
+      </c>
+      <c r="U655" s="2" t="inlineStr"/>
+      <c r="V655" s="2" t="inlineStr"/>
+      <c r="W655" s="2" t="inlineStr">
+        <is>
+          <t>Christian Borg</t>
+        </is>
+      </c>
+      <c r="X655" s="2" t="inlineStr">
+        <is>
+          <t>Purchaser</t>
+        </is>
+      </c>
+      <c r="Y655" s="2" t="inlineStr"/>
+      <c r="Z655" s="2" t="inlineStr"/>
+      <c r="AA655" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/christianborgsthlm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="2" t="inlineStr">
+        <is>
+          <t>Iconic Wines Ab</t>
+        </is>
+      </c>
+      <c r="B656" s="2" t="inlineStr">
+        <is>
+          <t>Iconic Wines Ab</t>
+        </is>
+      </c>
+      <c r="C656" s="2" t="inlineStr">
+        <is>
+          <t>25194</t>
+        </is>
+      </c>
+      <c r="D656" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E656" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F656" s="2" t="inlineStr">
+        <is>
+          <t>Stockholms län</t>
+        </is>
+      </c>
+      <c r="G656" s="2" t="inlineStr">
+        <is>
+          <t>4A Blasieholmsgatan</t>
+        </is>
+      </c>
+      <c r="H656" s="2" t="inlineStr">
+        <is>
+          <t>111 48</t>
+        </is>
+      </c>
+      <c r="I656" s="2" t="inlineStr">
+        <is>
+          <t>https://www.iconicwines.se</t>
+        </is>
+      </c>
+      <c r="J656" s="2" t="inlineStr"/>
+      <c r="K656" s="2" t="inlineStr"/>
+      <c r="L656" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M656" s="2" t="inlineStr"/>
+      <c r="N656" s="2" t="inlineStr">
+        <is>
+          <t>info@iconicwines.se</t>
+        </is>
+      </c>
+      <c r="O656" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 518 067 43</t>
+        </is>
+      </c>
+      <c r="P656" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q656" s="2" t="inlineStr">
+        <is>
+          <t>5590130471</t>
+        </is>
+      </c>
+      <c r="R656" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/iconic-wines/</t>
+        </is>
+      </c>
+      <c r="S656" s="2" t="inlineStr"/>
+      <c r="T656" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/iconic_wines/</t>
+        </is>
+      </c>
+      <c r="U656" s="2" t="inlineStr"/>
+      <c r="V656" s="2" t="inlineStr"/>
+      <c r="W656" s="2" t="inlineStr">
+        <is>
+          <t>Ulrika Olivestedt</t>
+        </is>
+      </c>
+      <c r="X656" s="2" t="inlineStr">
+        <is>
+          <t>Purchaser</t>
+        </is>
+      </c>
+      <c r="Y656" s="2" t="inlineStr"/>
+      <c r="Z656" s="2" t="inlineStr"/>
+      <c r="AA656" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ulrika-olivestedt-7b494371/</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="2" t="inlineStr">
+        <is>
+          <t>VD Wines AB</t>
+        </is>
+      </c>
+      <c r="B657" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VD Wines </t>
+        </is>
+      </c>
+      <c r="C657" s="2" t="inlineStr">
+        <is>
+          <t>34056</t>
+        </is>
+      </c>
+      <c r="D657" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E657" s="2" t="inlineStr">
+        <is>
+          <t>Hägersten</t>
+        </is>
+      </c>
+      <c r="F657" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="G657" s="2" t="inlineStr">
+        <is>
+          <t>Båtsmanskroken 30</t>
+        </is>
+      </c>
+      <c r="H657" s="2" t="inlineStr">
+        <is>
+          <t>129 40</t>
+        </is>
+      </c>
+      <c r="I657" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vdwines.se</t>
+        </is>
+      </c>
+      <c r="J657" s="2" t="inlineStr"/>
+      <c r="K657" s="2" t="inlineStr"/>
+      <c r="L657" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M657" s="2" t="inlineStr">
+        <is>
+          <t>224124</t>
+        </is>
+      </c>
+      <c r="N657" s="2" t="inlineStr">
+        <is>
+          <t>viktor@vdwines.se</t>
+        </is>
+      </c>
+      <c r="O657" s="2" t="inlineStr"/>
+      <c r="P657" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q657" s="2" t="inlineStr">
+        <is>
+          <t>5567348015</t>
+        </is>
+      </c>
+      <c r="R657" s="2" t="inlineStr"/>
+      <c r="S657" s="2" t="inlineStr"/>
+      <c r="T657" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vd.wines/</t>
+        </is>
+      </c>
+      <c r="U657" s="2" t="inlineStr"/>
+      <c r="V657" s="2" t="inlineStr"/>
+      <c r="W657" s="2" t="inlineStr">
+        <is>
+          <t>Viktor Djurdjevic</t>
+        </is>
+      </c>
+      <c r="X657" s="2" t="inlineStr">
+        <is>
+          <t>Ceo &amp; Founder</t>
+        </is>
+      </c>
+      <c r="Y657" s="2" t="inlineStr"/>
+      <c r="Z657" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA657" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/viktor-djurdjevic-61731157/</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="2" t="inlineStr">
+        <is>
+          <t>Portucastas Ab</t>
+        </is>
+      </c>
+      <c r="B658" s="2" t="inlineStr">
+        <is>
+          <t>Portucastas Ab</t>
+        </is>
+      </c>
+      <c r="C658" s="2" t="inlineStr">
+        <is>
+          <t>12793</t>
+        </is>
+      </c>
+      <c r="D658" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E658" s="2" t="inlineStr">
+        <is>
+          <t>Selånger District</t>
+        </is>
+      </c>
+      <c r="F658" s="2" t="inlineStr">
+        <is>
+          <t>Vasternorrland</t>
+        </is>
+      </c>
+      <c r="G658" s="2" t="inlineStr">
+        <is>
+          <t>Västerro 214</t>
+        </is>
+      </c>
+      <c r="H658" s="2" t="inlineStr">
+        <is>
+          <t>855 91</t>
+        </is>
+      </c>
+      <c r="I658" s="2" t="inlineStr">
+        <is>
+          <t>https://portucastas.se</t>
+        </is>
+      </c>
+      <c r="J658" s="2" t="inlineStr"/>
+      <c r="K658" s="2" t="inlineStr"/>
+      <c r="L658" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M658" s="2" t="inlineStr"/>
+      <c r="N658" s="2" t="inlineStr">
+        <is>
+          <t>info@portucastas.se</t>
+        </is>
+      </c>
+      <c r="O658" s="2" t="inlineStr">
+        <is>
+          <t>+351 289 030 928</t>
+        </is>
+      </c>
+      <c r="P658" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q658" s="2" t="inlineStr">
+        <is>
+          <t>5566467253</t>
+        </is>
+      </c>
+      <c r="R658" s="2" t="inlineStr"/>
+      <c r="S658" s="2" t="inlineStr"/>
+      <c r="T658" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/portucastas/</t>
+        </is>
+      </c>
+      <c r="U658" s="2" t="inlineStr"/>
+      <c r="V658" s="2" t="inlineStr"/>
+      <c r="W658" s="2" t="inlineStr">
+        <is>
+          <t>Mattias Strömquist</t>
+        </is>
+      </c>
+      <c r="X658" s="2" t="inlineStr">
+        <is>
+          <t>Ceo/ Sales</t>
+        </is>
+      </c>
+      <c r="Y658" s="2" t="inlineStr"/>
+      <c r="Z658" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA658" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mattias-str%C3%B6mquist-09bab5153/</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="2" t="inlineStr">
+        <is>
+          <t>Vinia Sweden Ab</t>
+        </is>
+      </c>
+      <c r="B659" s="2" t="inlineStr">
+        <is>
+          <t>Vinia Sweden Ab</t>
+        </is>
+      </c>
+      <c r="C659" s="2" t="inlineStr">
+        <is>
+          <t>12846</t>
+        </is>
+      </c>
+      <c r="D659" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E659" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F659" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G659" s="2" t="inlineStr">
+        <is>
+          <t>8 Gyllenstiernsgatan</t>
+        </is>
+      </c>
+      <c r="H659" s="2" t="inlineStr">
+        <is>
+          <t>115 26</t>
+        </is>
+      </c>
+      <c r="I659" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinia.se</t>
+        </is>
+      </c>
+      <c r="J659" s="2" t="inlineStr"/>
+      <c r="K659" s="2" t="inlineStr"/>
+      <c r="L659" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M659" s="2" t="inlineStr"/>
+      <c r="N659" s="2" t="inlineStr">
+        <is>
+          <t>info@vinia.se</t>
+        </is>
+      </c>
+      <c r="O659" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 732 59 95</t>
+        </is>
+      </c>
+      <c r="P659" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q659" s="2" t="inlineStr">
+        <is>
+          <t>5566906052</t>
+        </is>
+      </c>
+      <c r="R659" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinia-sweden-ab/</t>
+        </is>
+      </c>
+      <c r="S659" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Vinia-127868873799/</t>
+        </is>
+      </c>
+      <c r="T659" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viniasweden</t>
+        </is>
+      </c>
+      <c r="U659" s="2" t="inlineStr"/>
+      <c r="V659" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC7hui03EocS48wWL4cxSNUg</t>
+        </is>
+      </c>
+      <c r="W659" s="2" t="inlineStr">
+        <is>
+          <t>Per Engström</t>
+        </is>
+      </c>
+      <c r="X659" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y659" s="2" t="inlineStr"/>
+      <c r="Z659" s="2" t="inlineStr"/>
+      <c r="AA659" s="2" t="inlineStr">
+        <is>
+          <t>https://se.linkedin.com/pub/per-engstrom/3/283/b12</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="2" t="inlineStr">
+        <is>
+          <t>Vinia Sweden Ab</t>
+        </is>
+      </c>
+      <c r="B660" s="2" t="inlineStr">
+        <is>
+          <t>Vinia Sweden Ab</t>
+        </is>
+      </c>
+      <c r="C660" s="2" t="inlineStr">
+        <is>
+          <t>12846</t>
+        </is>
+      </c>
+      <c r="D660" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E660" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F660" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G660" s="2" t="inlineStr">
+        <is>
+          <t>8 Gyllenstiernsgatan</t>
+        </is>
+      </c>
+      <c r="H660" s="2" t="inlineStr">
+        <is>
+          <t>115 26</t>
+        </is>
+      </c>
+      <c r="I660" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinia.se</t>
+        </is>
+      </c>
+      <c r="J660" s="2" t="inlineStr"/>
+      <c r="K660" s="2" t="inlineStr"/>
+      <c r="L660" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M660" s="2" t="inlineStr"/>
+      <c r="N660" s="2" t="inlineStr">
+        <is>
+          <t>info@vinia.se</t>
+        </is>
+      </c>
+      <c r="O660" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 732 59 95</t>
+        </is>
+      </c>
+      <c r="P660" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q660" s="2" t="inlineStr">
+        <is>
+          <t>5566906052</t>
+        </is>
+      </c>
+      <c r="R660" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinia-sweden-ab/</t>
+        </is>
+      </c>
+      <c r="S660" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Vinia-127868873799/</t>
+        </is>
+      </c>
+      <c r="T660" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viniasweden</t>
+        </is>
+      </c>
+      <c r="U660" s="2" t="inlineStr"/>
+      <c r="V660" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC7hui03EocS48wWL4cxSNUg</t>
+        </is>
+      </c>
+      <c r="W660" s="2" t="inlineStr">
+        <is>
+          <t>Christina Nedfors</t>
+        </is>
+      </c>
+      <c r="X660" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager/ Administrations</t>
+        </is>
+      </c>
+      <c r="Y660" s="2" t="inlineStr"/>
+      <c r="Z660" s="2" t="inlineStr"/>
+      <c r="AA660" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/christina-nedfors-332629264/</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="2" t="inlineStr">
+        <is>
+          <t>Ward Wines Ab</t>
+        </is>
+      </c>
+      <c r="B661" s="2" t="inlineStr">
+        <is>
+          <t>Ward Wines Ab</t>
+        </is>
+      </c>
+      <c r="C661" s="2" t="inlineStr">
+        <is>
+          <t>12871</t>
+        </is>
+      </c>
+      <c r="D661" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E661" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F661" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G661" s="2" t="inlineStr">
+        <is>
+          <t>87D Östermalmsgatan</t>
+        </is>
+      </c>
+      <c r="H661" s="2" t="inlineStr">
+        <is>
+          <t>115 34</t>
+        </is>
+      </c>
+      <c r="I661" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wardwines.se</t>
+        </is>
+      </c>
+      <c r="J661" s="2" t="inlineStr"/>
+      <c r="K661" s="2" t="inlineStr"/>
+      <c r="L661" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M661" s="2" t="inlineStr"/>
+      <c r="N661" s="2" t="inlineStr">
+        <is>
+          <t>info@wardwines.se</t>
+        </is>
+      </c>
+      <c r="O661" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 511 698 30</t>
+        </is>
+      </c>
+      <c r="P661" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="Q661" s="2" t="inlineStr">
+        <is>
+          <t>5565055737</t>
+        </is>
+      </c>
+      <c r="R661" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ward-wines-ab/</t>
+        </is>
+      </c>
+      <c r="S661" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WardWines.AB</t>
+        </is>
+      </c>
+      <c r="T661" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ward_wines_vanner</t>
+        </is>
+      </c>
+      <c r="U661" s="2" t="inlineStr"/>
+      <c r="V661" s="2" t="inlineStr"/>
+      <c r="W661" s="2" t="inlineStr">
+        <is>
+          <t>Lisa Persson</t>
+        </is>
+      </c>
+      <c r="X661" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y661" s="2" t="inlineStr"/>
+      <c r="Z661" s="2" t="inlineStr"/>
+      <c r="AA661" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lisa-persson-b5635a27/</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="2" t="inlineStr">
+        <is>
+          <t>Ward Wines Ab</t>
+        </is>
+      </c>
+      <c r="B662" s="2" t="inlineStr">
+        <is>
+          <t>Ward Wines Ab</t>
+        </is>
+      </c>
+      <c r="C662" s="2" t="inlineStr">
+        <is>
+          <t>12871</t>
+        </is>
+      </c>
+      <c r="D662" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E662" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F662" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm County</t>
+        </is>
+      </c>
+      <c r="G662" s="2" t="inlineStr">
+        <is>
+          <t>87D Östermalmsgatan</t>
+        </is>
+      </c>
+      <c r="H662" s="2" t="inlineStr">
+        <is>
+          <t>115 34</t>
+        </is>
+      </c>
+      <c r="I662" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wardwines.se</t>
+        </is>
+      </c>
+      <c r="J662" s="2" t="inlineStr"/>
+      <c r="K662" s="2" t="inlineStr"/>
+      <c r="L662" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M662" s="2" t="inlineStr"/>
+      <c r="N662" s="2" t="inlineStr">
+        <is>
+          <t>info@wardwines.se</t>
+        </is>
+      </c>
+      <c r="O662" s="2" t="inlineStr">
+        <is>
+          <t>+46 8 511 698 30</t>
+        </is>
+      </c>
+      <c r="P662" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="Q662" s="2" t="inlineStr">
+        <is>
+          <t>5565055737</t>
+        </is>
+      </c>
+      <c r="R662" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ward-wines-ab/</t>
+        </is>
+      </c>
+      <c r="S662" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WardWines.AB</t>
+        </is>
+      </c>
+      <c r="T662" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ward_wines_vanner</t>
+        </is>
+      </c>
+      <c r="U662" s="2" t="inlineStr"/>
+      <c r="V662" s="2" t="inlineStr"/>
+      <c r="W662" s="2" t="inlineStr">
+        <is>
+          <t>Malin Keyser</t>
+        </is>
+      </c>
+      <c r="X662" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y662" s="2" t="inlineStr"/>
+      <c r="Z662" s="2" t="inlineStr"/>
+      <c r="AA662" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/malin-keyser-8258298/</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="2" t="inlineStr">
+        <is>
+          <t>Hübsch Vinhandel Ab</t>
+        </is>
+      </c>
+      <c r="B663" s="2" t="inlineStr">
+        <is>
+          <t>Hübsch Vinhandel Ab</t>
+        </is>
+      </c>
+      <c r="C663" s="2" t="inlineStr">
+        <is>
+          <t>25195</t>
+        </is>
+      </c>
+      <c r="D663" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E663" s="2" t="inlineStr">
+        <is>
+          <t>Bromma</t>
+        </is>
+      </c>
+      <c r="F663" s="2" t="inlineStr">
+        <is>
+          <t>Stockholms län</t>
+        </is>
+      </c>
+      <c r="G663" s="2" t="inlineStr">
+        <is>
+          <t>63 Doktor Abrahams Väg</t>
+        </is>
+      </c>
+      <c r="H663" s="2" t="inlineStr">
+        <is>
+          <t>168 59</t>
+        </is>
+      </c>
+      <c r="I663" s="2" t="inlineStr">
+        <is>
+          <t>https://hubschvinhandel.se</t>
+        </is>
+      </c>
+      <c r="J663" s="2" t="inlineStr"/>
+      <c r="K663" s="2" t="inlineStr"/>
+      <c r="L663" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M663" s="2" t="inlineStr"/>
+      <c r="N663" s="2" t="inlineStr">
+        <is>
+          <t>info@hubschvinhandel.se</t>
+        </is>
+      </c>
+      <c r="O663" s="2" t="inlineStr"/>
+      <c r="P663" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q663" s="2" t="inlineStr">
+        <is>
+          <t>5569489098</t>
+        </is>
+      </c>
+      <c r="R663" s="2" t="inlineStr"/>
+      <c r="S663" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hubschvinhandel</t>
+        </is>
+      </c>
+      <c r="T663" s="2" t="inlineStr"/>
+      <c r="U663" s="2" t="inlineStr"/>
+      <c r="V663" s="2" t="inlineStr"/>
+      <c r="W663" s="2" t="inlineStr">
+        <is>
+          <t>Göran Hübsch</t>
+        </is>
+      </c>
+      <c r="X663" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y663" s="2" t="inlineStr"/>
+      <c r="Z663" s="2" t="inlineStr"/>
+      <c r="AA663" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
